--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6513A7EA-C43C-4802-A171-B76AFDADF265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AFBD33-1EEF-4F5C-8939-AE3990C0D9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -1005,7 +1005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1017,59 +1017,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1086,18 +1053,27 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1418,1902 +1394,1902 @@
   <cols>
     <col min="1" max="1" width="12.31640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.31640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="40.54296875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="40.54296875" style="11" customWidth="1"/>
     <col min="4" max="4" width="50.6796875" style="4" customWidth="1"/>
     <col min="5" max="5" width="21.76953125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="24" t="s">
         <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="11"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="11"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="11"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="11"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="10" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="10" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" ht="24.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="24" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="11"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="10" t="s">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="10" t="s">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="10" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="10" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="10" t="s">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="10" t="s">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A21" s="14"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16" t="s">
+      <c r="A21" s="20"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20" t="s">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="18"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20" t="s">
+      <c r="A24" s="21"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="18"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="20" t="s">
+      <c r="A26" s="21"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="18"/>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="20" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="18"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="18"/>
+      <c r="E28" s="21"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="20" t="s">
+      <c r="A29" s="21"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="18"/>
+      <c r="E29" s="21"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="20" t="s">
+      <c r="A30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="18"/>
+      <c r="E30" s="21"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A32" s="14"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="16" t="s">
+      <c r="A32" s="20"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="20"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A33" s="14"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="16" t="s">
+      <c r="A33" s="20"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="20"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A34" s="14"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="16" t="s">
+      <c r="A34" s="20"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="14"/>
+      <c r="E34" s="20"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A35" s="14"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="16" t="s">
+      <c r="A35" s="20"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="E35" s="14"/>
+      <c r="E35" s="20"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="20" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="18"/>
+      <c r="E37" s="21"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="20" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="18"/>
+      <c r="E38" s="21"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A40" s="14"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="16" t="s">
+      <c r="A40" s="20"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="14"/>
+      <c r="E40" s="20"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A41" s="14"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="16" t="s">
+      <c r="A41" s="20"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="14"/>
+      <c r="E41" s="20"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A42" s="14"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="16" t="s">
+      <c r="A42" s="20"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="14"/>
+      <c r="E42" s="20"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A43" s="14"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="16" t="s">
+      <c r="A43" s="20"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="14"/>
+      <c r="E43" s="20"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="20" t="s">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="18"/>
+      <c r="E45" s="21"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="20" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="18"/>
+      <c r="E46" s="21"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A48" s="14"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="16" t="s">
+      <c r="A48" s="20"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="14"/>
-    </row>
-    <row r="49" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="18" t="s">
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A49" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="18"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20" t="s">
+    <row r="50" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A50" s="21"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="18"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A52" s="14"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="16" t="s">
+      <c r="A52" s="20"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E52" s="14"/>
+      <c r="E52" s="20"/>
     </row>
     <row r="53" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="14"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="16" t="s">
+      <c r="A53" s="20"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E53" s="14"/>
+      <c r="E53" s="20"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A54" s="14"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="16" t="s">
+      <c r="A54" s="20"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="14"/>
-    </row>
-    <row r="55" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="18" t="s">
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A55" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="18"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="20" t="s">
+    <row r="56" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A56" s="21"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="E56" s="18"/>
-    </row>
-    <row r="57" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="20" t="s">
+      <c r="E56" s="21"/>
+    </row>
+    <row r="57" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A57" s="21"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E57" s="18"/>
-    </row>
-    <row r="58" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20" t="s">
+      <c r="E57" s="21"/>
+    </row>
+    <row r="58" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="18"/>
-    </row>
-    <row r="59" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="18"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20" t="s">
+      <c r="E58" s="21"/>
+    </row>
+    <row r="59" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A59" s="21"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="18"/>
+      <c r="E59" s="21"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A61" s="14"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="16" t="s">
+      <c r="A61" s="20"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="14"/>
+      <c r="E61" s="20"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A63" s="18"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="20" t="s">
+      <c r="A63" s="21"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E63" s="18"/>
+      <c r="E63" s="21"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A64" s="18"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="20" t="s">
+      <c r="A64" s="21"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="18"/>
+      <c r="E64" s="21"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A65" s="18"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="20" t="s">
+      <c r="A65" s="21"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="18"/>
+      <c r="E65" s="21"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A66" s="18"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="20" t="s">
+      <c r="A66" s="21"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="18"/>
+      <c r="E66" s="21"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A67" s="18"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="20" t="s">
+      <c r="A67" s="21"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="18"/>
+      <c r="E67" s="21"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A68" s="18"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="20" t="s">
+      <c r="A68" s="21"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="18"/>
+      <c r="E68" s="21"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A69" s="18"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="20" t="s">
+      <c r="A69" s="21"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="18"/>
+      <c r="E69" s="21"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A70" s="18"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="20" t="s">
+      <c r="A70" s="21"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="18"/>
+      <c r="E70" s="21"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A71" s="18"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="20" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="18"/>
+      <c r="E71" s="21"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D72" s="16" t="s">
+      <c r="D72" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A73" s="14"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="16" t="s">
+      <c r="A73" s="20"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E73" s="14"/>
+      <c r="E73" s="20"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A74" s="14"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="16" t="s">
+      <c r="A74" s="20"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E74" s="14"/>
+      <c r="E74" s="20"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A75" s="14"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="16" t="s">
+      <c r="A75" s="20"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A76" s="14"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="16" t="s">
+      <c r="A76" s="20"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E76" s="14"/>
+      <c r="E76" s="20"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A77" s="18" t="s">
+      <c r="A77" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="19" t="s">
+      <c r="B77" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D77" s="20" t="s">
+      <c r="D77" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A78" s="18"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="20" t="s">
+      <c r="A78" s="21"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="18"/>
+      <c r="E78" s="21"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A79" s="18"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="20" t="s">
+      <c r="A79" s="21"/>
+      <c r="B79" s="22"/>
+      <c r="C79" s="22"/>
+      <c r="D79" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="18"/>
+      <c r="E79" s="21"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D80" s="16" t="s">
+      <c r="D80" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A81" s="14"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="16" t="s">
+      <c r="A81" s="20"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E81" s="14"/>
+      <c r="E81" s="20"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A82" s="14"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="16" t="s">
+      <c r="A82" s="20"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E82" s="14"/>
+      <c r="E82" s="20"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A83" s="14"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="16" t="s">
+      <c r="A83" s="20"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E83" s="14"/>
+      <c r="E83" s="20"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A84" s="14"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="16" t="s">
+      <c r="A84" s="20"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E84" s="14"/>
+      <c r="E84" s="20"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B85" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D85" s="20" t="s">
+      <c r="D85" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A86" s="18"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="20" t="s">
+      <c r="A86" s="21"/>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E86" s="18"/>
+      <c r="E86" s="21"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A87" s="18"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="20" t="s">
+      <c r="A87" s="21"/>
+      <c r="B87" s="22"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="E87" s="18"/>
+      <c r="E87" s="21"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B88" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D88" s="16" t="s">
+      <c r="D88" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A89" s="14"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="16" t="s">
+      <c r="A89" s="20"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="14"/>
+      <c r="E89" s="20"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="10" t="s">
+      <c r="A91" s="21"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="23"/>
+      <c r="D91" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="8"/>
+      <c r="E91" s="21"/>
     </row>
     <row r="92" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="10" t="s">
+      <c r="A92" s="21"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E92" s="8"/>
+      <c r="E92" s="21"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A93" s="5" t="s">
+      <c r="A93" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="24" t="s">
         <v>122</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E93" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A94" s="5"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="11"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="24"/>
       <c r="D94" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E94" s="5"/>
+      <c r="E94" s="20"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A95" s="5"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="11"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="24"/>
       <c r="D95" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E95" s="5"/>
+      <c r="E95" s="20"/>
     </row>
     <row r="96" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="8"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="10" t="s">
+      <c r="A97" s="21"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E97" s="8"/>
+      <c r="E97" s="21"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A98" s="8"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="12"/>
-      <c r="D98" s="10" t="s">
+      <c r="A98" s="21"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E98" s="8"/>
+      <c r="E98" s="21"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A99" s="5" t="s">
+      <c r="A99" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="24" t="s">
         <v>213</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E99" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A100" s="5"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="11"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="24"/>
       <c r="D100" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E100" s="5"/>
+      <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A101" s="5"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="11"/>
+      <c r="A101" s="20"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="24"/>
       <c r="D101" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="E101" s="5"/>
+      <c r="E101" s="20"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A102" s="5"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="11"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="24"/>
       <c r="D102" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E102" s="5"/>
+      <c r="E102" s="20"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A103" s="5"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="11"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="24"/>
       <c r="D103" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E103" s="5"/>
+      <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A104" s="5"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="11"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="24"/>
       <c r="D104" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E104" s="5"/>
+      <c r="E104" s="20"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A105" s="5"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="11"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="24"/>
       <c r="D105" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E105" s="5"/>
+      <c r="E105" s="20"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A106" s="18" t="s">
+      <c r="A106" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="19" t="s">
+      <c r="B106" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="19" t="s">
+      <c r="C106" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D106" s="20" t="s">
+      <c r="D106" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="18" t="s">
+      <c r="E106" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A107" s="18"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-      <c r="D107" s="20" t="s">
+      <c r="A107" s="21"/>
+      <c r="B107" s="22"/>
+      <c r="C107" s="22"/>
+      <c r="D107" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="18"/>
+      <c r="E107" s="21"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A108" s="18"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-      <c r="D108" s="20" t="s">
+      <c r="A108" s="21"/>
+      <c r="B108" s="22"/>
+      <c r="C108" s="22"/>
+      <c r="D108" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="18"/>
+      <c r="E108" s="21"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A109" s="18"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-      <c r="D109" s="20" t="s">
+      <c r="A109" s="21"/>
+      <c r="B109" s="22"/>
+      <c r="C109" s="22"/>
+      <c r="D109" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E109" s="18"/>
+      <c r="E109" s="21"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A110" s="18"/>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-      <c r="D110" s="20" t="s">
+      <c r="A110" s="21"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E110" s="18"/>
+      <c r="E110" s="21"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A111" s="18"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="20" t="s">
+      <c r="A111" s="21"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="18"/>
+      <c r="E111" s="21"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D112" s="16" t="s">
+      <c r="D112" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E112" s="14" t="s">
+      <c r="E112" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A113" s="14"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="17"/>
-      <c r="D113" s="16" t="s">
+      <c r="A113" s="20"/>
+      <c r="B113" s="19"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E113" s="14"/>
+      <c r="E113" s="20"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A114" s="14"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="16" t="s">
+      <c r="A114" s="20"/>
+      <c r="B114" s="19"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E114" s="14"/>
+      <c r="E114" s="20"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A115" s="14"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="16" t="s">
+      <c r="A115" s="20"/>
+      <c r="B115" s="19"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E115" s="14"/>
+      <c r="E115" s="20"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A116" s="14"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="16" t="s">
+      <c r="A116" s="20"/>
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E116" s="14"/>
+      <c r="E116" s="20"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A117" s="18" t="s">
+      <c r="A117" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="D117" s="20" t="s">
+      <c r="D117" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="18" t="s">
+      <c r="E117" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A118" s="18"/>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-      <c r="D118" s="20" t="s">
+      <c r="A118" s="21"/>
+      <c r="B118" s="22"/>
+      <c r="C118" s="22"/>
+      <c r="D118" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="18"/>
+      <c r="E118" s="21"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A119" s="18"/>
-      <c r="B119" s="19"/>
-      <c r="C119" s="19"/>
-      <c r="D119" s="20" t="s">
+      <c r="A119" s="21"/>
+      <c r="B119" s="22"/>
+      <c r="C119" s="22"/>
+      <c r="D119" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E119" s="29"/>
+      <c r="E119" s="8"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A120" s="18"/>
-      <c r="B120" s="19"/>
-      <c r="C120" s="19"/>
-      <c r="D120" s="20" t="s">
+      <c r="A120" s="21"/>
+      <c r="B120" s="22"/>
+      <c r="C120" s="22"/>
+      <c r="D120" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E120" s="18" t="s">
+      <c r="E120" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A121" s="18"/>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-      <c r="D121" s="20" t="s">
+      <c r="A121" s="21"/>
+      <c r="B121" s="22"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E121" s="18"/>
+      <c r="E121" s="21"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A122" s="18"/>
-      <c r="B122" s="19"/>
-      <c r="C122" s="19"/>
-      <c r="D122" s="20" t="s">
+      <c r="A122" s="21"/>
+      <c r="B122" s="22"/>
+      <c r="C122" s="22"/>
+      <c r="D122" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E122" s="18"/>
+      <c r="E122" s="21"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B123" s="17" t="s">
+      <c r="B123" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D123" s="16" t="s">
+      <c r="D123" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E123" s="14" t="s">
+      <c r="E123" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A124" s="14"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="16" t="s">
+      <c r="A124" s="20"/>
+      <c r="B124" s="19"/>
+      <c r="C124" s="19"/>
+      <c r="D124" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E124" s="14"/>
+      <c r="E124" s="20"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A125" s="18" t="s">
+      <c r="A125" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="B125" s="19" t="s">
+      <c r="B125" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="D125" s="20" t="s">
+      <c r="D125" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E125" s="18" t="s">
+      <c r="E125" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A126" s="18"/>
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-      <c r="D126" s="20" t="s">
+      <c r="A126" s="21"/>
+      <c r="B126" s="22"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E126" s="18"/>
+      <c r="E126" s="21"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A127" s="18"/>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="20" t="s">
+      <c r="A127" s="21"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E127" s="18" t="s">
+      <c r="E127" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A128" s="18"/>
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="20" t="s">
+      <c r="A128" s="21"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="E128" s="18"/>
+      <c r="E128" s="21"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A129" s="18"/>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="20" t="s">
+      <c r="A129" s="21"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="E129" s="18"/>
+      <c r="E129" s="21"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A130" s="18"/>
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-      <c r="D130" s="20" t="s">
+      <c r="A130" s="21"/>
+      <c r="B130" s="22"/>
+      <c r="C130" s="22"/>
+      <c r="D130" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="E130" s="18"/>
+      <c r="E130" s="21"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B131" s="17" t="s">
+      <c r="B131" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D131" s="16" t="s">
+      <c r="D131" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E131" s="14" t="s">
+      <c r="E131" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A132" s="14"/>
-      <c r="B132" s="17"/>
-      <c r="C132" s="15"/>
-      <c r="D132" s="16" t="s">
+      <c r="A132" s="20"/>
+      <c r="B132" s="19"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E132" s="14"/>
+      <c r="E132" s="20"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A133" s="18" t="s">
+      <c r="A133" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B133" s="19" t="s">
+      <c r="B133" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="19" t="s">
+      <c r="C133" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="D133" s="20" t="s">
+      <c r="D133" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E133" s="18" t="s">
+      <c r="E133" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A134" s="18"/>
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
-      <c r="D134" s="20" t="s">
+      <c r="A134" s="21"/>
+      <c r="B134" s="22"/>
+      <c r="C134" s="22"/>
+      <c r="D134" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="E134" s="18"/>
+      <c r="E134" s="21"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A135" s="14" t="s">
+      <c r="A135" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="B135" s="17" t="s">
+      <c r="B135" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C135" s="17" t="s">
+      <c r="C135" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D135" s="16" t="s">
+      <c r="D135" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="E135" s="14" t="s">
+      <c r="E135" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A136" s="14"/>
-      <c r="B136" s="17"/>
-      <c r="C136" s="17"/>
-      <c r="D136" s="16" t="s">
+      <c r="A136" s="20"/>
+      <c r="B136" s="19"/>
+      <c r="C136" s="19"/>
+      <c r="D136" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E136" s="14"/>
+      <c r="E136" s="20"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A137" s="14"/>
-      <c r="B137" s="17"/>
-      <c r="C137" s="17"/>
-      <c r="D137" s="16" t="s">
+      <c r="A137" s="20"/>
+      <c r="B137" s="19"/>
+      <c r="C137" s="19"/>
+      <c r="D137" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E137" s="21"/>
+      <c r="E137" s="20" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A138" s="14"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="17"/>
-      <c r="D138" s="16" t="s">
+      <c r="A138" s="20"/>
+      <c r="B138" s="19"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="E138" s="14" t="s">
+      <c r="E138" s="20"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A139" s="20"/>
+      <c r="B139" s="19"/>
+      <c r="C139" s="19"/>
+      <c r="D139" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" s="20"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A140" s="20"/>
+      <c r="B140" s="19"/>
+      <c r="C140" s="19"/>
+      <c r="D140" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E140" s="20"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A141" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B141" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E141" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A142" s="21"/>
+      <c r="B142" s="22"/>
+      <c r="C142" s="23"/>
+      <c r="D142" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E142" s="21"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A143" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A144" s="20"/>
+      <c r="B144" s="19"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E144" s="20"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A145" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B145" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C145" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E145" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A146" s="21"/>
+      <c r="B146" s="22"/>
+      <c r="C146" s="22"/>
+      <c r="D146" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E146" s="21"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A147" s="21"/>
+      <c r="B147" s="22"/>
+      <c r="C147" s="22"/>
+      <c r="D147" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E147" s="21"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A148" s="21"/>
+      <c r="B148" s="22"/>
+      <c r="C148" s="22"/>
+      <c r="D148" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E148" s="21"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A149" s="21"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E149" s="21"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A150" s="21"/>
+      <c r="B150" s="22"/>
+      <c r="C150" s="22"/>
+      <c r="D150" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E150" s="21"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A151" s="21"/>
+      <c r="B151" s="22"/>
+      <c r="C151" s="22"/>
+      <c r="D151" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E151" s="21"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A152" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E152" s="20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A139" s="14"/>
-      <c r="B139" s="17"/>
-      <c r="C139" s="17"/>
-      <c r="D139" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="E139" s="14"/>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A140" s="14"/>
-      <c r="B140" s="17"/>
-      <c r="C140" s="17"/>
-      <c r="D140" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="E140" s="14"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A141" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B141" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D141" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="E141" s="18" t="s">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A153" s="20"/>
+      <c r="B153" s="19"/>
+      <c r="C153" s="19"/>
+      <c r="D153" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E153" s="20"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A154" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B154" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C154" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E154" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A142" s="18"/>
-      <c r="B142" s="19"/>
-      <c r="C142" s="31"/>
-      <c r="D142" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="E142" s="18"/>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A143" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C143" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="D143" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="E143" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A144" s="14"/>
-      <c r="B144" s="17"/>
-      <c r="C144" s="17"/>
-      <c r="D144" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="E144" s="14"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A145" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="D145" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="E145" s="18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A146" s="18"/>
-      <c r="B146" s="19"/>
-      <c r="C146" s="19"/>
-      <c r="D146" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E146" s="18"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A147" s="18"/>
-      <c r="B147" s="19"/>
-      <c r="C147" s="19"/>
-      <c r="D147" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="E147" s="18"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A148" s="18"/>
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
-      <c r="D148" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E148" s="18"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A149" s="18"/>
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-      <c r="D149" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="E149" s="18"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A150" s="18"/>
-      <c r="B150" s="19"/>
-      <c r="C150" s="19"/>
-      <c r="D150" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="E150" s="18"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A151" s="18"/>
-      <c r="B151" s="19"/>
-      <c r="C151" s="19"/>
-      <c r="D151" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="E151" s="18"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A152" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B152" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="C152" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="D152" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="E152" s="14" t="s">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A155" s="21"/>
+      <c r="B155" s="22"/>
+      <c r="C155" s="22"/>
+      <c r="D155" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E155" s="21"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A156" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E156" s="20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A153" s="14"/>
-      <c r="B153" s="17"/>
-      <c r="C153" s="17"/>
-      <c r="D153" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E153" s="14"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A154" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="D154" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E154" s="18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A155" s="18"/>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
-      <c r="D155" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E155" s="18"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A156" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B156" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="C156" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="D156" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="E156" s="14" t="s">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A157" s="20"/>
+      <c r="B157" s="19"/>
+      <c r="C157" s="19"/>
+      <c r="D157" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E157" s="20"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A158" s="20"/>
+      <c r="B158" s="19"/>
+      <c r="C158" s="19"/>
+      <c r="D158" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E158" s="20"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A159" s="20"/>
+      <c r="B159" s="19"/>
+      <c r="C159" s="19"/>
+      <c r="D159" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E159" s="20"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A160" s="20"/>
+      <c r="B160" s="19"/>
+      <c r="C160" s="19"/>
+      <c r="D160" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E160" s="20"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A161" s="20"/>
+      <c r="B161" s="19"/>
+      <c r="C161" s="19"/>
+      <c r="D161" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E161" s="20"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A162" s="20"/>
+      <c r="B162" s="19"/>
+      <c r="C162" s="19"/>
+      <c r="D162" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E162" s="20"/>
+    </row>
+    <row r="163" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A163" s="20"/>
+      <c r="B163" s="19"/>
+      <c r="C163" s="19"/>
+      <c r="D163" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="E163" s="20"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A164" s="20"/>
+      <c r="B164" s="19"/>
+      <c r="C164" s="19"/>
+      <c r="D164" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E164" s="20"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A165" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B165" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C165" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E165" s="21" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A157" s="14"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="17"/>
-      <c r="D157" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="E157" s="14"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A158" s="14"/>
-      <c r="B158" s="17"/>
-      <c r="C158" s="17"/>
-      <c r="D158" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="E158" s="14"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A159" s="14"/>
-      <c r="B159" s="17"/>
-      <c r="C159" s="17"/>
-      <c r="D159" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="E159" s="14"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A160" s="14"/>
-      <c r="B160" s="17"/>
-      <c r="C160" s="17"/>
-      <c r="D160" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E160" s="14"/>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A161" s="14"/>
-      <c r="B161" s="17"/>
-      <c r="C161" s="17"/>
-      <c r="D161" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="E161" s="14"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A162" s="14"/>
-      <c r="B162" s="17"/>
-      <c r="C162" s="17"/>
-      <c r="D162" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="E162" s="14"/>
-    </row>
-    <row r="163" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A163" s="14"/>
-      <c r="B163" s="17"/>
-      <c r="C163" s="17"/>
-      <c r="D163" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="E163" s="14"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A164" s="14"/>
-      <c r="B164" s="17"/>
-      <c r="C164" s="17"/>
-      <c r="D164" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E164" s="14"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A165" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B165" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="C165" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="D165" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="E165" s="18" t="s">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A166" s="21"/>
+      <c r="B166" s="22"/>
+      <c r="C166" s="22"/>
+      <c r="D166" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E166" s="21"/>
+    </row>
+    <row r="167" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A167" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="B167" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C167" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E167" s="20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A166" s="18"/>
-      <c r="B166" s="19"/>
-      <c r="C166" s="19"/>
-      <c r="D166" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="E166" s="18"/>
-    </row>
-    <row r="167" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A167" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B167" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="C167" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="D167" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="E167" s="14" t="s">
-        <v>29</v>
-      </c>
-    </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A168" s="14"/>
-      <c r="B168" s="17"/>
-      <c r="C168" s="17"/>
-      <c r="D168" s="16" t="s">
+      <c r="A168" s="20"/>
+      <c r="B168" s="19"/>
+      <c r="C168" s="19"/>
+      <c r="D168" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E168" s="14"/>
+      <c r="E168" s="20"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A169" s="14"/>
-      <c r="B169" s="17"/>
-      <c r="C169" s="17"/>
-      <c r="D169" s="16" t="s">
+      <c r="A169" s="20"/>
+      <c r="B169" s="19"/>
+      <c r="C169" s="19"/>
+      <c r="D169" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E169" s="14"/>
+      <c r="E169" s="20"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A170" s="14"/>
-      <c r="B170" s="17"/>
-      <c r="C170" s="17"/>
-      <c r="D170" s="16" t="s">
+      <c r="A170" s="20"/>
+      <c r="B170" s="19"/>
+      <c r="C170" s="19"/>
+      <c r="D170" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E170" s="14"/>
+      <c r="E170" s="20"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A171" s="14"/>
-      <c r="B171" s="17"/>
-      <c r="C171" s="17"/>
-      <c r="D171" s="16" t="s">
+      <c r="A171" s="20"/>
+      <c r="B171" s="19"/>
+      <c r="C171" s="19"/>
+      <c r="D171" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E171" s="14"/>
+      <c r="E171" s="20"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A172" s="14"/>
-      <c r="B172" s="17"/>
-      <c r="C172" s="17"/>
-      <c r="D172" s="16" t="s">
+      <c r="A172" s="20"/>
+      <c r="B172" s="19"/>
+      <c r="C172" s="19"/>
+      <c r="D172" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E172" s="14"/>
+      <c r="E172" s="20"/>
     </row>
     <row r="173" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A173" s="2" t="s">
@@ -3322,7 +3298,7 @@
       <c r="B173" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C173" s="13" t="s">
+      <c r="C173" s="11" t="s">
         <v>263</v>
       </c>
       <c r="D173" s="4" t="s">
@@ -3333,71 +3309,148 @@
       </c>
     </row>
     <row r="174" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A174" s="21" t="s">
+      <c r="A174" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B174" s="22" t="s">
+      <c r="B174" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C174" s="28" t="s">
+      <c r="C174" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="D174" s="16" t="s">
+      <c r="D174" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E174" s="21" t="s">
+      <c r="E174" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A176" s="17" t="s">
+      <c r="A176" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="B176" s="17"/>
-      <c r="C176" s="17"/>
-      <c r="D176" s="17"/>
-      <c r="E176" s="17"/>
+      <c r="B176" s="19"/>
+      <c r="C176" s="19"/>
+      <c r="D176" s="19"/>
+      <c r="E176" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="E167:E172"/>
-    <mergeCell ref="C167:C172"/>
-    <mergeCell ref="B167:B172"/>
-    <mergeCell ref="A167:A172"/>
-    <mergeCell ref="C156:C164"/>
-    <mergeCell ref="B156:B164"/>
-    <mergeCell ref="A156:A164"/>
-    <mergeCell ref="E156:E164"/>
-    <mergeCell ref="E165:E166"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="E145:E151"/>
-    <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B145:B151"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="A135:A140"/>
-    <mergeCell ref="B135:B140"/>
-    <mergeCell ref="C135:C140"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="E138:E140"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="E137:E140"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C22:C30"/>
+    <mergeCell ref="E22:E30"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B19"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="C13:C19"/>
+    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="E51:E54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="A62:A71"/>
+    <mergeCell ref="B62:B71"/>
+    <mergeCell ref="C62:C71"/>
+    <mergeCell ref="E62:E71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="A99:A105"/>
+    <mergeCell ref="B99:B105"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="E99:E105"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="E85:E87"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="C117:C122"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="A117:A122"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="E106:E111"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="C112:C116"/>
     <mergeCell ref="C123:C124"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="A123:A124"/>
@@ -3415,120 +3468,43 @@
     <mergeCell ref="C131:C132"/>
     <mergeCell ref="E131:E132"/>
     <mergeCell ref="A131:A132"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="C117:C122"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="A117:A122"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="E106:E111"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="A99:A105"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="E99:E105"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="E93:E95"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="A62:A71"/>
-    <mergeCell ref="B62:B71"/>
-    <mergeCell ref="C62:C71"/>
-    <mergeCell ref="E62:E71"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="E51:E54"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C22:C30"/>
-    <mergeCell ref="E22:E30"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="E13:E19"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="B135:B140"/>
+    <mergeCell ref="C135:C140"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="E145:E151"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B145:B151"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="E167:E172"/>
+    <mergeCell ref="C167:C172"/>
+    <mergeCell ref="B167:B172"/>
+    <mergeCell ref="A167:A172"/>
+    <mergeCell ref="C156:C164"/>
+    <mergeCell ref="B156:B164"/>
+    <mergeCell ref="A156:A164"/>
+    <mergeCell ref="E156:E164"/>
+    <mergeCell ref="E165:E166"/>
+    <mergeCell ref="C165:C166"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="A165:A166"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AFBD33-1EEF-4F5C-8939-AE3990C0D9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F183BD84-9CFE-402E-AB59-5702E9411D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -1058,22 +1058,22 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1417,1879 +1417,1879 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A3" s="20"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="24"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="21"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A4" s="20"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="24"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A5" s="20"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="24"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A6" s="20"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="24"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" ht="24.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="19" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="24"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="E11" s="20"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="E12" s="20"/>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>214</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="23"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" s="21"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A21" s="20"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="24"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="24" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
       <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="21"/>
+      <c r="E23" s="23"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="21"/>
+      <c r="E24" s="23"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="21"/>
+      <c r="E25" s="23"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="21"/>
+      <c r="E26" s="23"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
       <c r="D27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="21"/>
+      <c r="E27" s="23"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A28" s="21"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="21"/>
+      <c r="E28" s="23"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A29" s="21"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
       <c r="D29" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="21"/>
+      <c r="E29" s="23"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A30" s="21"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="21"/>
+      <c r="E30" s="23"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A32" s="20"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="20"/>
+      <c r="E32" s="21"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A33" s="20"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
       <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="20"/>
+      <c r="E33" s="21"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A34" s="20"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="20"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A35" s="20"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="E35" s="20"/>
+      <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="24" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A37" s="21"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
       <c r="D37" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="21"/>
+      <c r="E37" s="23"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
       <c r="D38" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="21"/>
+      <c r="E38" s="23"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A40" s="20"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="20"/>
+      <c r="E40" s="21"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A41" s="20"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="20"/>
+      <c r="E41" s="21"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A42" s="20"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
       <c r="D42" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="20"/>
+      <c r="E42" s="21"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A43" s="20"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
       <c r="D43" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="20"/>
+      <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="24" t="s">
         <v>108</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="E44" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="22"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="24"/>
       <c r="D45" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="21"/>
+      <c r="E45" s="23"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="22"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24"/>
       <c r="D46" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="21"/>
+      <c r="E46" s="23"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A48" s="20"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="24"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="19"/>
       <c r="D48" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="20"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="24" t="s">
         <v>81</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="E49" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="21"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="21"/>
+      <c r="E50" s="23"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="20" t="s">
         <v>69</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A52" s="20"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E52" s="20"/>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="20"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E53" s="20"/>
+      <c r="E53" s="21"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A54" s="20"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
       <c r="D54" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="20"/>
+      <c r="E54" s="21"/>
     </row>
     <row r="55" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="24" t="s">
         <v>72</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="21"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="23"/>
     </row>
     <row r="57" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="21"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E57" s="21"/>
+      <c r="E57" s="23"/>
     </row>
     <row r="58" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="21"/>
+      <c r="E58" s="23"/>
     </row>
     <row r="59" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="21"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="21"/>
+      <c r="E59" s="23"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="C60" s="19" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A61" s="20"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="24"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="19"/>
       <c r="D61" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="20"/>
+      <c r="E61" s="21"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="24" t="s">
         <v>98</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A63" s="21"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E63" s="21"/>
+      <c r="E63" s="23"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A64" s="21"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="21"/>
+      <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A65" s="21"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="21"/>
+      <c r="E65" s="23"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A66" s="21"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="21"/>
+      <c r="E66" s="23"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A67" s="21"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="21"/>
+      <c r="E67" s="23"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A68" s="21"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="21"/>
+      <c r="E68" s="23"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A69" s="21"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="21"/>
+      <c r="E69" s="23"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A70" s="21"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="21"/>
+      <c r="E70" s="23"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A71" s="21"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="21"/>
+      <c r="E71" s="23"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="20" t="s">
         <v>102</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A73" s="20"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
+      <c r="A73" s="21"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
       <c r="D73" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E73" s="20"/>
+      <c r="E73" s="21"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A74" s="20"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
+      <c r="A74" s="21"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E74" s="20"/>
+      <c r="E74" s="21"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A75" s="20"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
+      <c r="A75" s="21"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
       <c r="D75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E75" s="20" t="s">
+      <c r="E75" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A76" s="20"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
+      <c r="A76" s="21"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E76" s="20"/>
+      <c r="E76" s="21"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A77" s="21" t="s">
+      <c r="A77" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B77" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="22" t="s">
+      <c r="C77" s="24" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="21" t="s">
+      <c r="E77" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A78" s="21"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="23"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A79" s="21"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="22"/>
+      <c r="A79" s="23"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="21"/>
+      <c r="E79" s="23"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="19" t="s">
+      <c r="B80" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E80" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A81" s="20"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
+      <c r="A81" s="21"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E81" s="20"/>
+      <c r="E81" s="21"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A82" s="20"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
+      <c r="A82" s="21"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E82" s="20"/>
+      <c r="E82" s="21"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A83" s="20"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
+      <c r="A83" s="21"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
       <c r="D83" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E83" s="20"/>
+      <c r="E83" s="21"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A84" s="20"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
+      <c r="A84" s="21"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E84" s="20"/>
+      <c r="E84" s="21"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A85" s="21" t="s">
+      <c r="A85" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="B85" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="22" t="s">
+      <c r="C85" s="24" t="s">
         <v>107</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E85" s="21" t="s">
+      <c r="E85" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A86" s="21"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="22"/>
+      <c r="A86" s="23"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="24"/>
       <c r="D86" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E86" s="21"/>
+      <c r="E86" s="23"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A87" s="21"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="22"/>
+      <c r="A87" s="23"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
       <c r="D87" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="E87" s="21"/>
+      <c r="E87" s="23"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A88" s="20" t="s">
+      <c r="A88" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="24" t="s">
+      <c r="C88" s="19" t="s">
         <v>32</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="20" t="s">
+      <c r="E88" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A89" s="20"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="24"/>
+      <c r="A89" s="21"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="19"/>
       <c r="D89" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="20"/>
+      <c r="E89" s="21"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="22" t="s">
+      <c r="B90" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="22" t="s">
         <v>281</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="21" t="s">
+      <c r="E90" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A91" s="21"/>
-      <c r="B91" s="22"/>
-      <c r="C91" s="23"/>
+      <c r="A91" s="23"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="22"/>
       <c r="D91" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="21"/>
+      <c r="E91" s="23"/>
     </row>
     <row r="92" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="21"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="23"/>
+      <c r="A92" s="23"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="22"/>
       <c r="D92" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E92" s="21"/>
+      <c r="E92" s="23"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A93" s="20" t="s">
+      <c r="A93" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B93" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="24" t="s">
+      <c r="C93" s="19" t="s">
         <v>122</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E93" s="20" t="s">
+      <c r="E93" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A94" s="20"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="24"/>
+      <c r="A94" s="21"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="19"/>
       <c r="D94" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E94" s="20"/>
+      <c r="E94" s="21"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A95" s="20"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="24"/>
+      <c r="A95" s="21"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="19"/>
       <c r="D95" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E95" s="20"/>
+      <c r="E95" s="21"/>
     </row>
     <row r="96" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="21" t="s">
+      <c r="A96" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="22" t="s">
+      <c r="B96" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="22" t="s">
         <v>127</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="21" t="s">
+      <c r="E96" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="21"/>
-      <c r="B97" s="22"/>
-      <c r="C97" s="23"/>
+      <c r="A97" s="23"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="22"/>
       <c r="D97" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E97" s="21"/>
+      <c r="E97" s="23"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A98" s="21"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="23"/>
+      <c r="A98" s="23"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="22"/>
       <c r="D98" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E98" s="21"/>
+      <c r="E98" s="23"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A99" s="20" t="s">
+      <c r="A99" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B99" s="19" t="s">
+      <c r="B99" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="24" t="s">
+      <c r="C99" s="19" t="s">
         <v>213</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E99" s="20" t="s">
+      <c r="E99" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A100" s="20"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="24"/>
+      <c r="A100" s="21"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="19"/>
       <c r="D100" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E100" s="20"/>
+      <c r="E100" s="21"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A101" s="20"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="24"/>
+      <c r="A101" s="21"/>
+      <c r="B101" s="20"/>
+      <c r="C101" s="19"/>
       <c r="D101" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="E101" s="20"/>
+      <c r="E101" s="21"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A102" s="20"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="24"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="19"/>
       <c r="D102" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E102" s="20"/>
+      <c r="E102" s="21"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A103" s="20"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="24"/>
+      <c r="A103" s="21"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="19"/>
       <c r="D103" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E103" s="20"/>
+      <c r="E103" s="21"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A104" s="20"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="24"/>
+      <c r="A104" s="21"/>
+      <c r="B104" s="20"/>
+      <c r="C104" s="19"/>
       <c r="D104" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E104" s="20"/>
+      <c r="E104" s="21"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A105" s="20"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="24"/>
+      <c r="A105" s="21"/>
+      <c r="B105" s="20"/>
+      <c r="C105" s="19"/>
       <c r="D105" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E105" s="20"/>
+      <c r="E105" s="21"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="22" t="s">
+      <c r="C106" s="24" t="s">
         <v>146</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="21" t="s">
+      <c r="E106" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A107" s="21"/>
-      <c r="B107" s="22"/>
-      <c r="C107" s="22"/>
+      <c r="A107" s="23"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
       <c r="D107" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="21"/>
+      <c r="E107" s="23"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A108" s="21"/>
-      <c r="B108" s="22"/>
-      <c r="C108" s="22"/>
+      <c r="A108" s="23"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="24"/>
       <c r="D108" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="21"/>
+      <c r="E108" s="23"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A109" s="21"/>
-      <c r="B109" s="22"/>
-      <c r="C109" s="22"/>
+      <c r="A109" s="23"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
       <c r="D109" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E109" s="21"/>
+      <c r="E109" s="23"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A110" s="21"/>
-      <c r="B110" s="22"/>
-      <c r="C110" s="22"/>
+      <c r="A110" s="23"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="24"/>
       <c r="D110" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E110" s="21"/>
+      <c r="E110" s="23"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A111" s="21"/>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
+      <c r="A111" s="23"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
       <c r="D111" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="21"/>
+      <c r="E111" s="23"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A112" s="20" t="s">
+      <c r="A112" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="B112" s="19" t="s">
+      <c r="B112" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C112" s="20" t="s">
         <v>169</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E112" s="20" t="s">
+      <c r="E112" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A113" s="20"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
+      <c r="A113" s="21"/>
+      <c r="B113" s="20"/>
+      <c r="C113" s="20"/>
       <c r="D113" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E113" s="20"/>
+      <c r="E113" s="21"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A114" s="20"/>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
+      <c r="A114" s="21"/>
+      <c r="B114" s="20"/>
+      <c r="C114" s="20"/>
       <c r="D114" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E114" s="20"/>
+      <c r="E114" s="21"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A115" s="20"/>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
+      <c r="A115" s="21"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
       <c r="D115" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E115" s="20"/>
+      <c r="E115" s="21"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A116" s="20"/>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
+      <c r="A116" s="21"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="20"/>
       <c r="D116" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E116" s="20"/>
+      <c r="E116" s="21"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="B117" s="22" t="s">
+      <c r="B117" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="22" t="s">
+      <c r="C117" s="24" t="s">
         <v>176</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="21" t="s">
+      <c r="E117" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A118" s="21"/>
-      <c r="B118" s="22"/>
-      <c r="C118" s="22"/>
+      <c r="A118" s="23"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="24"/>
       <c r="D118" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="21"/>
+      <c r="E118" s="23"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A119" s="21"/>
-      <c r="B119" s="22"/>
-      <c r="C119" s="22"/>
+      <c r="A119" s="23"/>
+      <c r="B119" s="24"/>
+      <c r="C119" s="24"/>
       <c r="D119" s="9" t="s">
         <v>249</v>
       </c>
       <c r="E119" s="8"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A120" s="21"/>
-      <c r="B120" s="22"/>
-      <c r="C120" s="22"/>
+      <c r="A120" s="23"/>
+      <c r="B120" s="24"/>
+      <c r="C120" s="24"/>
       <c r="D120" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E120" s="21" t="s">
+      <c r="E120" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A121" s="21"/>
-      <c r="B121" s="22"/>
-      <c r="C121" s="22"/>
+      <c r="A121" s="23"/>
+      <c r="B121" s="24"/>
+      <c r="C121" s="24"/>
       <c r="D121" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E121" s="21"/>
+      <c r="E121" s="23"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A122" s="21"/>
-      <c r="B122" s="22"/>
-      <c r="C122" s="22"/>
+      <c r="A122" s="23"/>
+      <c r="B122" s="24"/>
+      <c r="C122" s="24"/>
       <c r="D122" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E122" s="21"/>
+      <c r="E122" s="23"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A123" s="20" t="s">
+      <c r="A123" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B123" s="19" t="s">
+      <c r="B123" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C123" s="19" t="s">
+      <c r="C123" s="20" t="s">
         <v>184</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E123" s="20" t="s">
+      <c r="E123" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A124" s="20"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
+      <c r="A124" s="21"/>
+      <c r="B124" s="20"/>
+      <c r="C124" s="20"/>
       <c r="D124" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E124" s="20"/>
+      <c r="E124" s="21"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B125" s="22" t="s">
+      <c r="B125" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C125" s="22" t="s">
+      <c r="C125" s="24" t="s">
         <v>175</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E125" s="21" t="s">
+      <c r="E125" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A126" s="21"/>
-      <c r="B126" s="22"/>
-      <c r="C126" s="22"/>
+      <c r="A126" s="23"/>
+      <c r="B126" s="24"/>
+      <c r="C126" s="24"/>
       <c r="D126" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E126" s="21"/>
+      <c r="E126" s="23"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A127" s="21"/>
-      <c r="B127" s="22"/>
-      <c r="C127" s="22"/>
+      <c r="A127" s="23"/>
+      <c r="B127" s="24"/>
+      <c r="C127" s="24"/>
       <c r="D127" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E127" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="E127" s="23"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A128" s="21"/>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22"/>
+      <c r="A128" s="23"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="24"/>
       <c r="D128" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="E128" s="21"/>
+      <c r="E128" s="23" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A129" s="21"/>
-      <c r="B129" s="22"/>
-      <c r="C129" s="22"/>
+      <c r="A129" s="23"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="24"/>
       <c r="D129" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="E129" s="21"/>
+      <c r="E129" s="23"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A130" s="21"/>
-      <c r="B130" s="22"/>
-      <c r="C130" s="22"/>
+      <c r="A130" s="23"/>
+      <c r="B130" s="24"/>
+      <c r="C130" s="24"/>
       <c r="D130" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="E130" s="21"/>
+      <c r="E130" s="23"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A131" s="20" t="s">
+      <c r="A131" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="24" t="s">
+      <c r="C131" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E131" s="20" t="s">
+      <c r="E131" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A132" s="20"/>
-      <c r="B132" s="19"/>
-      <c r="C132" s="24"/>
+      <c r="A132" s="21"/>
+      <c r="B132" s="20"/>
+      <c r="C132" s="19"/>
       <c r="D132" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E132" s="20"/>
+      <c r="E132" s="21"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B133" s="22" t="s">
+      <c r="B133" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="22" t="s">
+      <c r="C133" s="24" t="s">
         <v>184</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E133" s="21" t="s">
+      <c r="E133" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A134" s="21"/>
-      <c r="B134" s="22"/>
-      <c r="C134" s="22"/>
+      <c r="A134" s="23"/>
+      <c r="B134" s="24"/>
+      <c r="C134" s="24"/>
       <c r="D134" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="E134" s="21"/>
+      <c r="E134" s="23"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A135" s="20" t="s">
+      <c r="A135" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B135" s="19" t="s">
+      <c r="B135" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="C135" s="19" t="s">
+      <c r="C135" s="20" t="s">
         <v>193</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="E135" s="20" t="s">
+      <c r="E135" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A136" s="20"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
+      <c r="A136" s="21"/>
+      <c r="B136" s="20"/>
+      <c r="C136" s="20"/>
       <c r="D136" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E136" s="20"/>
+      <c r="E136" s="21"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A137" s="20"/>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
+      <c r="A137" s="21"/>
+      <c r="B137" s="20"/>
+      <c r="C137" s="20"/>
       <c r="D137" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E137" s="20" t="s">
-        <v>29</v>
-      </c>
+      <c r="E137" s="21"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A138" s="20"/>
-      <c r="B138" s="19"/>
-      <c r="C138" s="19"/>
+      <c r="A138" s="21"/>
+      <c r="B138" s="20"/>
+      <c r="C138" s="20"/>
       <c r="D138" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="E138" s="20"/>
+      <c r="E138" s="21" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A139" s="20"/>
-      <c r="B139" s="19"/>
-      <c r="C139" s="19"/>
+      <c r="A139" s="21"/>
+      <c r="B139" s="20"/>
+      <c r="C139" s="20"/>
       <c r="D139" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="E139" s="20"/>
+      <c r="E139" s="21"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A140" s="20"/>
-      <c r="B140" s="19"/>
-      <c r="C140" s="19"/>
+      <c r="A140" s="21"/>
+      <c r="B140" s="20"/>
+      <c r="C140" s="20"/>
       <c r="D140" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E140" s="20"/>
+      <c r="E140" s="21"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A141" s="21" t="s">
+      <c r="A141" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="B141" s="22" t="s">
+      <c r="B141" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C141" s="23" t="s">
+      <c r="C141" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="E141" s="21" t="s">
+      <c r="E141" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A142" s="21"/>
-      <c r="B142" s="22"/>
-      <c r="C142" s="23"/>
+      <c r="A142" s="23"/>
+      <c r="B142" s="24"/>
+      <c r="C142" s="22"/>
       <c r="D142" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E142" s="21"/>
+      <c r="E142" s="23"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A143" s="20" t="s">
+      <c r="A143" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B143" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C143" s="19" t="s">
+      <c r="C143" s="20" t="s">
         <v>184</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E143" s="20" t="s">
+      <c r="E143" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A144" s="20"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="19"/>
+      <c r="A144" s="21"/>
+      <c r="B144" s="20"/>
+      <c r="C144" s="20"/>
       <c r="D144" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E144" s="20"/>
+      <c r="E144" s="21"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B145" s="22" t="s">
+      <c r="B145" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="C145" s="22" t="s">
+      <c r="C145" s="24" t="s">
         <v>211</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="E145" s="21" t="s">
+      <c r="E145" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A146" s="21"/>
-      <c r="B146" s="22"/>
-      <c r="C146" s="22"/>
+      <c r="A146" s="23"/>
+      <c r="B146" s="24"/>
+      <c r="C146" s="24"/>
       <c r="D146" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="E146" s="21"/>
+      <c r="E146" s="23"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A147" s="21"/>
-      <c r="B147" s="22"/>
-      <c r="C147" s="22"/>
+      <c r="A147" s="23"/>
+      <c r="B147" s="24"/>
+      <c r="C147" s="24"/>
       <c r="D147" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E147" s="21"/>
+      <c r="E147" s="23"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A148" s="21"/>
-      <c r="B148" s="22"/>
-      <c r="C148" s="22"/>
+      <c r="A148" s="23"/>
+      <c r="B148" s="24"/>
+      <c r="C148" s="24"/>
       <c r="D148" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E148" s="21"/>
+      <c r="E148" s="23"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A149" s="21"/>
-      <c r="B149" s="22"/>
-      <c r="C149" s="22"/>
+      <c r="A149" s="23"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
       <c r="D149" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E149" s="21"/>
+      <c r="E149" s="23"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A150" s="21"/>
-      <c r="B150" s="22"/>
-      <c r="C150" s="22"/>
+      <c r="A150" s="23"/>
+      <c r="B150" s="24"/>
+      <c r="C150" s="24"/>
       <c r="D150" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="E150" s="21"/>
+      <c r="E150" s="23"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A151" s="21"/>
-      <c r="B151" s="22"/>
-      <c r="C151" s="22"/>
+      <c r="A151" s="23"/>
+      <c r="B151" s="24"/>
+      <c r="C151" s="24"/>
       <c r="D151" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E151" s="21"/>
+      <c r="E151" s="23"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A152" s="20" t="s">
+      <c r="A152" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C152" s="19" t="s">
+      <c r="C152" s="20" t="s">
         <v>212</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E152" s="20" t="s">
+      <c r="E152" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A153" s="20"/>
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
+      <c r="A153" s="21"/>
+      <c r="B153" s="20"/>
+      <c r="C153" s="20"/>
       <c r="D153" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="E153" s="20"/>
+      <c r="E153" s="21"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="B154" s="22" t="s">
+      <c r="B154" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="C154" s="22" t="s">
+      <c r="C154" s="24" t="s">
         <v>233</v>
       </c>
       <c r="D154" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="E154" s="21" t="s">
+      <c r="E154" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A155" s="21"/>
-      <c r="B155" s="22"/>
-      <c r="C155" s="22"/>
+      <c r="A155" s="23"/>
+      <c r="B155" s="24"/>
+      <c r="C155" s="24"/>
       <c r="D155" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E155" s="21"/>
+      <c r="E155" s="23"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A156" s="20" t="s">
+      <c r="A156" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="B156" s="19" t="s">
+      <c r="B156" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="C156" s="19" t="s">
+      <c r="C156" s="20" t="s">
         <v>232</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E156" s="20" t="s">
+      <c r="E156" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A157" s="20"/>
-      <c r="B157" s="19"/>
-      <c r="C157" s="19"/>
+      <c r="A157" s="21"/>
+      <c r="B157" s="20"/>
+      <c r="C157" s="20"/>
       <c r="D157" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="E157" s="20"/>
+      <c r="E157" s="21"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A158" s="20"/>
-      <c r="B158" s="19"/>
-      <c r="C158" s="19"/>
+      <c r="A158" s="21"/>
+      <c r="B158" s="20"/>
+      <c r="C158" s="20"/>
       <c r="D158" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="E158" s="20"/>
+      <c r="E158" s="21"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A159" s="20"/>
-      <c r="B159" s="19"/>
-      <c r="C159" s="19"/>
+      <c r="A159" s="21"/>
+      <c r="B159" s="20"/>
+      <c r="C159" s="20"/>
       <c r="D159" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E159" s="20"/>
+      <c r="E159" s="21"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A160" s="20"/>
-      <c r="B160" s="19"/>
-      <c r="C160" s="19"/>
+      <c r="A160" s="21"/>
+      <c r="B160" s="20"/>
+      <c r="C160" s="20"/>
       <c r="D160" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="E160" s="20"/>
+      <c r="E160" s="21"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A161" s="20"/>
-      <c r="B161" s="19"/>
-      <c r="C161" s="19"/>
+      <c r="A161" s="21"/>
+      <c r="B161" s="20"/>
+      <c r="C161" s="20"/>
       <c r="D161" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E161" s="20"/>
+      <c r="E161" s="21"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A162" s="20"/>
-      <c r="B162" s="19"/>
-      <c r="C162" s="19"/>
+      <c r="A162" s="21"/>
+      <c r="B162" s="20"/>
+      <c r="C162" s="20"/>
       <c r="D162" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E162" s="20"/>
+      <c r="E162" s="21"/>
     </row>
     <row r="163" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A163" s="20"/>
-      <c r="B163" s="19"/>
-      <c r="C163" s="19"/>
+      <c r="A163" s="21"/>
+      <c r="B163" s="20"/>
+      <c r="C163" s="20"/>
       <c r="D163" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="E163" s="20"/>
+      <c r="E163" s="21"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A164" s="20"/>
-      <c r="B164" s="19"/>
-      <c r="C164" s="19"/>
+      <c r="A164" s="21"/>
+      <c r="B164" s="20"/>
+      <c r="C164" s="20"/>
       <c r="D164" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E164" s="20"/>
+      <c r="E164" s="21"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A165" s="21" t="s">
+      <c r="A165" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B165" s="22" t="s">
+      <c r="B165" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="C165" s="22" t="s">
+      <c r="C165" s="24" t="s">
         <v>231</v>
       </c>
       <c r="D165" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E165" s="21" t="s">
+      <c r="E165" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A166" s="21"/>
-      <c r="B166" s="22"/>
-      <c r="C166" s="22"/>
+      <c r="A166" s="23"/>
+      <c r="B166" s="24"/>
+      <c r="C166" s="24"/>
       <c r="D166" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="E166" s="21"/>
+      <c r="E166" s="23"/>
     </row>
     <row r="167" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A167" s="20" t="s">
+      <c r="A167" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="B167" s="19" t="s">
+      <c r="B167" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="C167" s="19" t="s">
+      <c r="C167" s="20" t="s">
         <v>242</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="E167" s="20" t="s">
+      <c r="E167" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A168" s="20"/>
-      <c r="B168" s="19"/>
-      <c r="C168" s="19"/>
+      <c r="A168" s="21"/>
+      <c r="B168" s="20"/>
+      <c r="C168" s="20"/>
       <c r="D168" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E168" s="20"/>
+      <c r="E168" s="21"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A169" s="20"/>
-      <c r="B169" s="19"/>
-      <c r="C169" s="19"/>
+      <c r="A169" s="21"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="20"/>
       <c r="D169" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E169" s="20"/>
+      <c r="E169" s="21"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A170" s="20"/>
-      <c r="B170" s="19"/>
-      <c r="C170" s="19"/>
+      <c r="A170" s="21"/>
+      <c r="B170" s="20"/>
+      <c r="C170" s="20"/>
       <c r="D170" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E170" s="20"/>
+      <c r="E170" s="21"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A171" s="20"/>
-      <c r="B171" s="19"/>
-      <c r="C171" s="19"/>
+      <c r="A171" s="21"/>
+      <c r="B171" s="20"/>
+      <c r="C171" s="20"/>
       <c r="D171" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E171" s="20"/>
+      <c r="E171" s="21"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A172" s="20"/>
-      <c r="B172" s="19"/>
-      <c r="C172" s="19"/>
+      <c r="A172" s="21"/>
+      <c r="B172" s="20"/>
+      <c r="C172" s="20"/>
       <c r="D172" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E172" s="20"/>
+      <c r="E172" s="21"/>
     </row>
     <row r="173" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A173" s="2" t="s">
@@ -3326,94 +3326,84 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A176" s="19" t="s">
+      <c r="A176" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="B176" s="19"/>
-      <c r="C176" s="19"/>
-      <c r="D176" s="19"/>
-      <c r="E176" s="19"/>
+      <c r="B176" s="20"/>
+      <c r="C176" s="20"/>
+      <c r="D176" s="20"/>
+      <c r="E176" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="E137:E140"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C22:C30"/>
-    <mergeCell ref="E22:E30"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="E13:E19"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="E51:E54"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="A62:A71"/>
-    <mergeCell ref="B62:B71"/>
-    <mergeCell ref="C62:C71"/>
-    <mergeCell ref="E62:E71"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="A99:A105"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="E99:E105"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="E167:E172"/>
+    <mergeCell ref="C167:C172"/>
+    <mergeCell ref="B167:B172"/>
+    <mergeCell ref="A167:A172"/>
+    <mergeCell ref="C156:C164"/>
+    <mergeCell ref="B156:B164"/>
+    <mergeCell ref="A156:A164"/>
+    <mergeCell ref="E156:E164"/>
+    <mergeCell ref="E165:E166"/>
+    <mergeCell ref="C165:C166"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="E145:E151"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B145:B151"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="B135:B140"/>
+    <mergeCell ref="C135:C140"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="E138:E140"/>
+    <mergeCell ref="E135:E137"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="E133:E134"/>
+    <mergeCell ref="B125:B130"/>
+    <mergeCell ref="C125:C130"/>
+    <mergeCell ref="A125:A130"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="E131:E132"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="E128:E130"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="C117:C122"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="A117:A122"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="E106:E111"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="C112:C116"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="E60:E61"/>
     <mergeCell ref="A88:A89"/>
@@ -3438,73 +3428,83 @@
     <mergeCell ref="E77:E79"/>
     <mergeCell ref="A80:A84"/>
     <mergeCell ref="B80:B84"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="C117:C122"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="A117:A122"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="E106:E111"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="E133:E134"/>
-    <mergeCell ref="B125:B130"/>
-    <mergeCell ref="C125:C130"/>
-    <mergeCell ref="E125:E126"/>
-    <mergeCell ref="E127:E130"/>
-    <mergeCell ref="A125:A130"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="E131:E132"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="A135:A140"/>
-    <mergeCell ref="B135:B140"/>
-    <mergeCell ref="C135:C140"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="E145:E151"/>
-    <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B145:B151"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="E167:E172"/>
-    <mergeCell ref="C167:C172"/>
-    <mergeCell ref="B167:B172"/>
-    <mergeCell ref="A167:A172"/>
-    <mergeCell ref="C156:C164"/>
-    <mergeCell ref="B156:B164"/>
-    <mergeCell ref="A156:A164"/>
-    <mergeCell ref="E156:E164"/>
-    <mergeCell ref="E165:E166"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="A99:A105"/>
+    <mergeCell ref="B99:B105"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="E99:E105"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="A62:A71"/>
+    <mergeCell ref="B62:B71"/>
+    <mergeCell ref="C62:C71"/>
+    <mergeCell ref="E62:E71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="E51:E54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C22:C30"/>
+    <mergeCell ref="E22:E30"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B19"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="C13:C19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F183BD84-9CFE-402E-AB59-5702E9411D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD96948-2E43-43C5-BAC3-75184ABEDA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="289">
   <si>
     <t>Feature ID</t>
   </si>
@@ -893,6 +893,18 @@
   </si>
   <si>
     <t>RTYPE-05-C: rs1_val cross rs2_val</t>
+  </si>
+  <si>
+    <t>Observe at End of Program **</t>
+  </si>
+  <si>
+    <t>Observe After Reset ***</t>
+  </si>
+  <si>
+    <t>** At the end of program, an illegal instruction (32'b0) is sent to trigger halt of the processor.</t>
+  </si>
+  <si>
+    <t>*** After reset, pipeline is emptied and should implement NOP correctly until getting filled by instructions.</t>
   </si>
 </sst>
 </file>
@@ -1389,14 +1401,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965CD32B-6EE1-4A11-9866-0D904F197471}">
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="12.31640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.31640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="40.54296875" style="11" customWidth="1"/>
     <col min="4" max="4" width="50.6796875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="21.76953125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.75">
@@ -2216,9 +2228,7 @@
       <c r="D75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E75" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="E75" s="21"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="21"/>
@@ -3076,7 +3086,7 @@
         <v>209</v>
       </c>
       <c r="E152" s="21" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.75">
@@ -3217,7 +3227,7 @@
         <v>234</v>
       </c>
       <c r="E165" s="23" t="s">
-        <v>29</v>
+        <v>285</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.75">
@@ -3322,7 +3332,7 @@
         <v>270</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>29</v>
+        <v>286</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
@@ -3334,8 +3344,28 @@
       <c r="D176" s="20"/>
       <c r="E176" s="20"/>
     </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A177" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B177" s="24"/>
+      <c r="C177" s="24"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A178" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B178" s="20"/>
+      <c r="C178" s="20"/>
+      <c r="D178" s="20"/>
+      <c r="E178" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="170">
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A178:E178"/>
     <mergeCell ref="A176:E176"/>
     <mergeCell ref="E167:E172"/>
     <mergeCell ref="C167:C172"/>
@@ -3420,8 +3450,6 @@
     <mergeCell ref="B85:B87"/>
     <mergeCell ref="C85:C87"/>
     <mergeCell ref="E85:E87"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="E75:E76"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C77:C79"/>
@@ -3453,6 +3481,11 @@
     <mergeCell ref="A72:A76"/>
     <mergeCell ref="B72:B76"/>
     <mergeCell ref="C72:C76"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="C22:C30"/>
+    <mergeCell ref="E22:E30"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B22:B30"/>
     <mergeCell ref="C55:C59"/>
     <mergeCell ref="E55:E59"/>
     <mergeCell ref="E49:E50"/>
@@ -3465,7 +3498,6 @@
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A55:A59"/>
     <mergeCell ref="B55:B59"/>
-    <mergeCell ref="E13:E19"/>
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="A39:A43"/>
     <mergeCell ref="E44:E46"/>
@@ -3494,10 +3526,6 @@
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C22:C30"/>
-    <mergeCell ref="E22:E30"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B22:B30"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="A10:A12"/>
@@ -3505,6 +3533,7 @@
     <mergeCell ref="B13:B19"/>
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="C13:C19"/>
+    <mergeCell ref="E13:E19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD96948-2E43-43C5-BAC3-75184ABEDA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFAC421-495E-4534-B554-6B0F8C05B6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="288">
   <si>
     <t>Feature ID</t>
   </si>
@@ -717,15 +717,6 @@
     <t>HAZARD-04-E: load stall followed by jump/branch</t>
   </si>
   <si>
-    <t>HAZARD-04-F: jump/branch followed by load stall</t>
-  </si>
-  <si>
-    <t>HAZARD-04-G: consecutive RAWs</t>
-  </si>
-  <si>
-    <t>HAZARD-04-I: consecutive jumps/branches</t>
-  </si>
-  <si>
     <t>OP-01</t>
   </si>
   <si>
@@ -874,9 +865,6 @@
   </si>
   <si>
     <t>STYPE-03-C: address wraps above top (out of memory range)</t>
-  </si>
-  <si>
-    <t>HAZARD-04-H: consecutive load stalls (2nd load instruction's rs1 is the same register as rd of the 1st load instruction)</t>
   </si>
   <si>
     <t>OP-01-B: op code is illegal and triggers halt</t>
@@ -905,6 +893,15 @@
   </si>
   <si>
     <t>*** After reset, pipeline is emptied and should implement NOP correctly until getting filled by instructions.</t>
+  </si>
+  <si>
+    <t>HAZARD-04-F: consecutive RAWs</t>
+  </si>
+  <si>
+    <t>HAZARD-04-G: consecutive load stalls (2nd load instruction's rs1 is the same register as rd of the 1st load instruction)</t>
+  </si>
+  <si>
+    <t>HAZARD-04-H: consecutive jumps/branches</t>
   </si>
 </sst>
 </file>
@@ -1069,8 +1066,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1079,13 +1076,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1401,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965CD32B-6EE1-4A11-9866-0D904F197471}">
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="12.31640625" style="2" customWidth="1"/>
@@ -1435,7 +1432,7 @@
       <c r="B2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="24" t="s">
         <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1448,7 +1445,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="21"/>
       <c r="B3" s="20"/>
-      <c r="C3" s="19"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1457,7 +1454,7 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="21"/>
       <c r="B4" s="20"/>
-      <c r="C4" s="19"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
@@ -1466,7 +1463,7 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="21"/>
       <c r="B5" s="20"/>
-      <c r="C5" s="19"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
@@ -1475,46 +1472,46 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="21"/>
       <c r="B6" s="20"/>
-      <c r="C6" s="19"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="22"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="22"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" spans="1:5" ht="24.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" s="21" t="s">
@@ -1523,7 +1520,7 @@
       <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="24" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -1536,91 +1533,91 @@
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" s="21"/>
       <c r="B11" s="20"/>
-      <c r="C11" s="19"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="21"/>
       <c r="B12" s="20"/>
-      <c r="C12" s="19"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>214</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="23"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E15" s="23"/>
+        <v>269</v>
+      </c>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="22"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="22"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="23"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="22"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="23"/>
+      <c r="E18" s="22"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="22"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="23"/>
+      <c r="E19" s="22"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="21" t="s">
@@ -1629,7 +1626,7 @@
       <c r="B20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -1642,100 +1639,100 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="19"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="19" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="23"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="23"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="23"/>
+      <c r="E25" s="22"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="23"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="23"/>
+      <c r="E27" s="22"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A28" s="23"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
       <c r="D28" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="23"/>
+      <c r="E28" s="22"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
       <c r="D29" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="23"/>
+      <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A30" s="23"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="23"/>
+      <c r="E30" s="22"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="21" t="s">
@@ -1786,44 +1783,44 @@
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
       <c r="D35" s="7" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
       <c r="D37" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="23"/>
+      <c r="E37" s="22"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A38" s="23"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
       <c r="D38" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="23"/>
+      <c r="E38" s="22"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="21" t="s">
@@ -1879,39 +1876,39 @@
       <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="19" t="s">
         <v>108</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="19"/>
       <c r="D45" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="23"/>
+      <c r="E45" s="22"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="24"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="19"/>
       <c r="D46" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="23"/>
+      <c r="E46" s="22"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="21" t="s">
@@ -1920,7 +1917,7 @@
       <c r="B47" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="7" t="s">
@@ -1933,37 +1930,37 @@
     <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="21"/>
       <c r="B48" s="20"/>
-      <c r="C48" s="19"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="7" t="s">
         <v>138</v>
       </c>
       <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="19" t="s">
         <v>81</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="23"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
       <c r="D50" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="23"/>
+      <c r="E50" s="22"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="21" t="s">
@@ -1987,7 +1984,7 @@
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
       <c r="D52" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E52" s="21"/>
     </row>
@@ -1996,7 +1993,7 @@
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
       <c r="D53" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E53" s="21"/>
     </row>
@@ -2010,57 +2007,57 @@
       <c r="E54" s="21"/>
     </row>
     <row r="55" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="19" t="s">
         <v>72</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="23"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
       <c r="D56" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E56" s="23"/>
+        <v>244</v>
+      </c>
+      <c r="E56" s="22"/>
     </row>
     <row r="57" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="23"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
       <c r="D57" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="E57" s="23"/>
+        <v>245</v>
+      </c>
+      <c r="E57" s="22"/>
     </row>
     <row r="58" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="23"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
       <c r="D58" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="23"/>
+      <c r="E58" s="22"/>
     </row>
     <row r="59" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="23"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
       <c r="D59" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="23"/>
+      <c r="E59" s="22"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="21" t="s">
@@ -2069,7 +2066,7 @@
       <c r="B60" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="24" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="7" t="s">
@@ -2082,109 +2079,109 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="21"/>
       <c r="B61" s="20"/>
-      <c r="C61" s="19"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="7" t="s">
         <v>141</v>
       </c>
       <c r="E61" s="21"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="19" t="s">
         <v>98</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="23" t="s">
+      <c r="E62" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A63" s="23"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
       <c r="D63" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E63" s="23"/>
+      <c r="E63" s="22"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A64" s="23"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
       <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="23"/>
+      <c r="E64" s="22"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A65" s="23"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
       <c r="D65" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="23"/>
+      <c r="E65" s="22"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A66" s="23"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
       <c r="D66" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="23"/>
+      <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A67" s="23"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
       <c r="D67" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="23"/>
+      <c r="E67" s="22"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A68" s="23"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
       <c r="D68" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="23"/>
+      <c r="E68" s="22"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A69" s="23"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
+      <c r="A69" s="22"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
       <c r="D69" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="23"/>
+      <c r="E69" s="22"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A70" s="23"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
+      <c r="A70" s="22"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
       <c r="D70" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="23"/>
+      <c r="E70" s="22"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A71" s="23"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
+      <c r="A71" s="22"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
       <c r="D71" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="23"/>
+      <c r="E71" s="22"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="21" t="s">
@@ -2240,39 +2237,39 @@
       <c r="E76" s="21"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="24" t="s">
+      <c r="B77" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="24" t="s">
+      <c r="C77" s="19" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="E77" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A78" s="23"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
       <c r="D78" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="23"/>
+      <c r="E78" s="22"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A79" s="23"/>
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
+      <c r="A79" s="22"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
       <c r="D79" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="23"/>
+      <c r="E79" s="22"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A80" s="21" t="s">
@@ -2328,39 +2325,39 @@
       <c r="E84" s="21"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A85" s="23" t="s">
+      <c r="A85" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="24" t="s">
+      <c r="B85" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="C85" s="19" t="s">
         <v>107</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E85" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E85" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A86" s="23"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="19"/>
       <c r="D86" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="E86" s="23"/>
+        <v>279</v>
+      </c>
+      <c r="E86" s="22"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A87" s="23"/>
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
       <c r="D87" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E87" s="23"/>
+        <v>280</v>
+      </c>
+      <c r="E87" s="22"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A88" s="21" t="s">
@@ -2369,7 +2366,7 @@
       <c r="B88" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" s="24" t="s">
         <v>32</v>
       </c>
       <c r="D88" s="7" t="s">
@@ -2382,46 +2379,46 @@
     <row r="89" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A89" s="21"/>
       <c r="B89" s="20"/>
-      <c r="C89" s="19"/>
+      <c r="C89" s="24"/>
       <c r="D89" s="7" t="s">
         <v>144</v>
       </c>
       <c r="E89" s="21"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="24" t="s">
+      <c r="B90" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="22" t="s">
-        <v>281</v>
+      <c r="C90" s="23" t="s">
+        <v>277</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A91" s="23"/>
-      <c r="B91" s="24"/>
-      <c r="C91" s="22"/>
+      <c r="A91" s="22"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="23"/>
       <c r="D91" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="23"/>
+      <c r="E91" s="22"/>
     </row>
     <row r="92" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="23"/>
-      <c r="B92" s="24"/>
-      <c r="C92" s="22"/>
+      <c r="A92" s="22"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="23"/>
       <c r="D92" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E92" s="23"/>
+      <c r="E92" s="22"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A93" s="21" t="s">
@@ -2430,7 +2427,7 @@
       <c r="B93" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="24" t="s">
         <v>122</v>
       </c>
       <c r="D93" s="7" t="s">
@@ -2443,7 +2440,7 @@
     <row r="94" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A94" s="21"/>
       <c r="B94" s="20"/>
-      <c r="C94" s="19"/>
+      <c r="C94" s="24"/>
       <c r="D94" s="7" t="s">
         <v>124</v>
       </c>
@@ -2452,46 +2449,46 @@
     <row r="95" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A95" s="21"/>
       <c r="B95" s="20"/>
-      <c r="C95" s="19"/>
+      <c r="C95" s="24"/>
       <c r="D95" s="7" t="s">
         <v>125</v>
       </c>
       <c r="E95" s="21"/>
     </row>
     <row r="96" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="24" t="s">
+      <c r="B96" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="22" t="s">
+      <c r="C96" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="23" t="s">
+      <c r="E96" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="23"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="22"/>
+      <c r="A97" s="22"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="23"/>
       <c r="D97" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="E97" s="23"/>
+        <v>274</v>
+      </c>
+      <c r="E97" s="22"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A98" s="23"/>
-      <c r="B98" s="24"/>
-      <c r="C98" s="22"/>
+      <c r="A98" s="22"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="23"/>
       <c r="D98" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E98" s="23"/>
+        <v>275</v>
+      </c>
+      <c r="E98" s="22"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A99" s="21" t="s">
@@ -2500,7 +2497,7 @@
       <c r="B99" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="24" t="s">
         <v>213</v>
       </c>
       <c r="D99" s="7" t="s">
@@ -2513,7 +2510,7 @@
     <row r="100" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A100" s="21"/>
       <c r="B100" s="20"/>
-      <c r="C100" s="19"/>
+      <c r="C100" s="24"/>
       <c r="D100" s="7" t="s">
         <v>131</v>
       </c>
@@ -2522,16 +2519,16 @@
     <row r="101" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A101" s="21"/>
       <c r="B101" s="20"/>
-      <c r="C101" s="19"/>
+      <c r="C101" s="24"/>
       <c r="D101" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E101" s="21"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A102" s="21"/>
       <c r="B102" s="20"/>
-      <c r="C102" s="19"/>
+      <c r="C102" s="24"/>
       <c r="D102" s="7" t="s">
         <v>132</v>
       </c>
@@ -2540,7 +2537,7 @@
     <row r="103" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A103" s="21"/>
       <c r="B103" s="20"/>
-      <c r="C103" s="19"/>
+      <c r="C103" s="24"/>
       <c r="D103" s="7" t="s">
         <v>133</v>
       </c>
@@ -2549,7 +2546,7 @@
     <row r="104" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A104" s="21"/>
       <c r="B104" s="20"/>
-      <c r="C104" s="19"/>
+      <c r="C104" s="24"/>
       <c r="D104" s="7" t="s">
         <v>134</v>
       </c>
@@ -2558,73 +2555,73 @@
     <row r="105" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A105" s="21"/>
       <c r="B105" s="20"/>
-      <c r="C105" s="19"/>
+      <c r="C105" s="24"/>
       <c r="D105" s="7" t="s">
         <v>135</v>
       </c>
       <c r="E105" s="21"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A106" s="23" t="s">
+      <c r="A106" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="24" t="s">
+      <c r="C106" s="19" t="s">
         <v>146</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="23" t="s">
+      <c r="E106" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A107" s="23"/>
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
+      <c r="A107" s="22"/>
+      <c r="B107" s="19"/>
+      <c r="C107" s="19"/>
       <c r="D107" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="23"/>
+      <c r="E107" s="22"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A108" s="23"/>
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
+      <c r="A108" s="22"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="19"/>
       <c r="D108" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="23"/>
+      <c r="E108" s="22"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A109" s="23"/>
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
+      <c r="A109" s="22"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="19"/>
       <c r="D109" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E109" s="23"/>
+      <c r="E109" s="22"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A110" s="23"/>
-      <c r="B110" s="24"/>
-      <c r="C110" s="24"/>
+      <c r="A110" s="22"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="19"/>
       <c r="D110" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E110" s="23"/>
+      <c r="E110" s="22"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A111" s="23"/>
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
+      <c r="A111" s="22"/>
+      <c r="B111" s="19"/>
+      <c r="C111" s="19"/>
       <c r="D111" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="23"/>
+      <c r="E111" s="22"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A112" s="21" t="s">
@@ -2680,68 +2677,68 @@
       <c r="E116" s="21"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A117" s="23" t="s">
+      <c r="A117" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="B117" s="24" t="s">
+      <c r="B117" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="24" t="s">
+      <c r="C117" s="19" t="s">
         <v>176</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="23" t="s">
+      <c r="E117" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A118" s="23"/>
-      <c r="B118" s="24"/>
-      <c r="C118" s="24"/>
+      <c r="A118" s="22"/>
+      <c r="B118" s="19"/>
+      <c r="C118" s="19"/>
       <c r="D118" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="23"/>
+      <c r="E118" s="22"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A119" s="23"/>
-      <c r="B119" s="24"/>
-      <c r="C119" s="24"/>
+      <c r="A119" s="22"/>
+      <c r="B119" s="19"/>
+      <c r="C119" s="19"/>
       <c r="D119" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E119" s="8"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A120" s="22"/>
+      <c r="B120" s="19"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E120" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A121" s="22"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E121" s="22"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A122" s="22"/>
+      <c r="B122" s="19"/>
+      <c r="C122" s="19"/>
+      <c r="D122" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E119" s="8"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A120" s="23"/>
-      <c r="B120" s="24"/>
-      <c r="C120" s="24"/>
-      <c r="D120" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E120" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A121" s="23"/>
-      <c r="B121" s="24"/>
-      <c r="C121" s="24"/>
-      <c r="D121" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E121" s="23"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A122" s="23"/>
-      <c r="B122" s="24"/>
-      <c r="C122" s="24"/>
-      <c r="D122" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E122" s="23"/>
+      <c r="E122" s="22"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A123" s="21" t="s">
@@ -2770,68 +2767,68 @@
       <c r="E124" s="21"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A125" s="23" t="s">
+      <c r="A125" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="B125" s="24" t="s">
+      <c r="B125" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C125" s="24" t="s">
+      <c r="C125" s="19" t="s">
         <v>175</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E125" s="23" t="s">
+      <c r="E125" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A126" s="23"/>
-      <c r="B126" s="24"/>
-      <c r="C126" s="24"/>
+      <c r="A126" s="22"/>
+      <c r="B126" s="19"/>
+      <c r="C126" s="19"/>
       <c r="D126" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E126" s="23"/>
+      <c r="E126" s="22"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A127" s="23"/>
-      <c r="B127" s="24"/>
-      <c r="C127" s="24"/>
+      <c r="A127" s="22"/>
+      <c r="B127" s="19"/>
+      <c r="C127" s="19"/>
       <c r="D127" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E127" s="22"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A128" s="22"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="19"/>
+      <c r="D128" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E128" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A129" s="22"/>
+      <c r="B129" s="19"/>
+      <c r="C129" s="19"/>
+      <c r="D129" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E129" s="22"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A130" s="22"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="19"/>
+      <c r="D130" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E127" s="23"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A128" s="23"/>
-      <c r="B128" s="24"/>
-      <c r="C128" s="24"/>
-      <c r="D128" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="E128" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A129" s="23"/>
-      <c r="B129" s="24"/>
-      <c r="C129" s="24"/>
-      <c r="D129" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E129" s="23"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A130" s="23"/>
-      <c r="B130" s="24"/>
-      <c r="C130" s="24"/>
-      <c r="D130" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E130" s="23"/>
+      <c r="E130" s="22"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A131" s="21" t="s">
@@ -2840,7 +2837,7 @@
       <c r="B131" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C131" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="7" t="s">
@@ -2853,37 +2850,37 @@
     <row r="132" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A132" s="21"/>
       <c r="B132" s="20"/>
-      <c r="C132" s="19"/>
+      <c r="C132" s="24"/>
       <c r="D132" s="7" t="s">
         <v>181</v>
       </c>
       <c r="E132" s="21"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A133" s="23" t="s">
+      <c r="A133" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="24" t="s">
+      <c r="C133" s="19" t="s">
         <v>184</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E133" s="23" t="s">
+      <c r="E133" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A134" s="23"/>
-      <c r="B134" s="24"/>
-      <c r="C134" s="24"/>
+      <c r="A134" s="22"/>
+      <c r="B134" s="19"/>
+      <c r="C134" s="19"/>
       <c r="D134" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="E134" s="23"/>
+      <c r="E134" s="22"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A135" s="21" t="s">
@@ -2916,7 +2913,7 @@
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
       <c r="D137" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E137" s="21"/>
     </row>
@@ -2925,7 +2922,7 @@
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
       <c r="D138" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E138" s="21" t="s">
         <v>29</v>
@@ -2936,7 +2933,7 @@
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
       <c r="D139" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E139" s="21"/>
     </row>
@@ -2945,35 +2942,35 @@
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
       <c r="D140" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E140" s="21"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A141" s="23" t="s">
+      <c r="A141" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="B141" s="24" t="s">
+      <c r="B141" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C141" s="22" t="s">
+      <c r="C141" s="23" t="s">
         <v>32</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="E141" s="23" t="s">
+      <c r="E141" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A142" s="23"/>
-      <c r="B142" s="24"/>
-      <c r="C142" s="22"/>
+      <c r="A142" s="22"/>
+      <c r="B142" s="19"/>
+      <c r="C142" s="23"/>
       <c r="D142" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E142" s="23"/>
+      <c r="E142" s="22"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A143" s="21" t="s">
@@ -3002,75 +2999,75 @@
       <c r="E144" s="21"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A145" s="23" t="s">
+      <c r="A145" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B145" s="24" t="s">
+      <c r="B145" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="C145" s="24" t="s">
+      <c r="C145" s="19" t="s">
         <v>211</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="E145" s="23" t="s">
+      <c r="E145" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A146" s="23"/>
-      <c r="B146" s="24"/>
-      <c r="C146" s="24"/>
+      <c r="A146" s="22"/>
+      <c r="B146" s="19"/>
+      <c r="C146" s="19"/>
       <c r="D146" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="E146" s="23"/>
+      <c r="E146" s="22"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A147" s="23"/>
-      <c r="B147" s="24"/>
-      <c r="C147" s="24"/>
+      <c r="A147" s="22"/>
+      <c r="B147" s="19"/>
+      <c r="C147" s="19"/>
       <c r="D147" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E147" s="23"/>
+      <c r="E147" s="22"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A148" s="23"/>
-      <c r="B148" s="24"/>
-      <c r="C148" s="24"/>
+      <c r="A148" s="22"/>
+      <c r="B148" s="19"/>
+      <c r="C148" s="19"/>
       <c r="D148" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E148" s="23"/>
+      <c r="E148" s="22"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A149" s="23"/>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
+      <c r="A149" s="22"/>
+      <c r="B149" s="19"/>
+      <c r="C149" s="19"/>
       <c r="D149" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E149" s="23"/>
+      <c r="E149" s="22"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A150" s="23"/>
-      <c r="B150" s="24"/>
-      <c r="C150" s="24"/>
+      <c r="A150" s="22"/>
+      <c r="B150" s="19"/>
+      <c r="C150" s="19"/>
       <c r="D150" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E150" s="23"/>
+        <v>262</v>
+      </c>
+      <c r="E150" s="22"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A151" s="23"/>
-      <c r="B151" s="24"/>
-      <c r="C151" s="24"/>
+      <c r="A151" s="22"/>
+      <c r="B151" s="19"/>
+      <c r="C151" s="19"/>
       <c r="D151" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="E151" s="23"/>
+        <v>263</v>
+      </c>
+      <c r="E151" s="22"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A152" s="21" t="s">
@@ -3099,30 +3096,30 @@
       <c r="E153" s="21"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A154" s="23" t="s">
+      <c r="A154" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="B154" s="24" t="s">
+      <c r="B154" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="C154" s="24" t="s">
-        <v>233</v>
+      <c r="C154" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="D154" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="E154" s="23" t="s">
+      <c r="E154" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A155" s="23"/>
-      <c r="B155" s="24"/>
-      <c r="C155" s="24"/>
+      <c r="A155" s="22"/>
+      <c r="B155" s="19"/>
+      <c r="C155" s="19"/>
       <c r="D155" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E155" s="23"/>
+      <c r="E155" s="22"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A156" s="21" t="s">
@@ -3132,7 +3129,7 @@
         <v>220</v>
       </c>
       <c r="C156" s="20" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>222</v>
@@ -3182,86 +3179,86 @@
       <c r="B161" s="20"/>
       <c r="C161" s="20"/>
       <c r="D161" s="7" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="E161" s="21"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A162" s="21"/>
       <c r="B162" s="20"/>
       <c r="C162" s="20"/>
-      <c r="D162" s="7" t="s">
-        <v>227</v>
+      <c r="D162" s="18" t="s">
+        <v>286</v>
       </c>
       <c r="E162" s="21"/>
     </row>
-    <row r="163" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A163" s="21"/>
       <c r="B163" s="20"/>
       <c r="C163" s="20"/>
-      <c r="D163" s="18" t="s">
-        <v>279</v>
+      <c r="D163" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="E163" s="21"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A164" s="21"/>
-      <c r="B164" s="20"/>
-      <c r="C164" s="20"/>
-      <c r="D164" s="7" t="s">
+      <c r="A164" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C164" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="E164" s="21"/>
+      <c r="D164" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E164" s="22" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A165" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="B165" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="C165" s="24" t="s">
-        <v>231</v>
-      </c>
+      <c r="A165" s="22"/>
+      <c r="B165" s="19"/>
+      <c r="C165" s="19"/>
       <c r="D165" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E165" s="22"/>
+    </row>
+    <row r="166" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A166" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B166" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="C166" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D166" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E165" s="23" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A166" s="23"/>
-      <c r="B166" s="24"/>
-      <c r="C166" s="24"/>
-      <c r="D166" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="E166" s="23"/>
-    </row>
-    <row r="167" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A167" s="21" t="s">
+      <c r="E166" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A167" s="21"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="20"/>
+      <c r="D167" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B167" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="C167" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E167" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="E167" s="21"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A168" s="21"/>
       <c r="B168" s="20"/>
       <c r="C168" s="20"/>
       <c r="D168" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E168" s="21"/>
     </row>
@@ -3270,7 +3267,7 @@
       <c r="B169" s="20"/>
       <c r="C169" s="20"/>
       <c r="D169" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E169" s="21"/>
     </row>
@@ -3279,7 +3276,7 @@
       <c r="B170" s="20"/>
       <c r="C170" s="20"/>
       <c r="D170" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E170" s="21"/>
     </row>
@@ -3288,192 +3285,109 @@
       <c r="B171" s="20"/>
       <c r="C171" s="20"/>
       <c r="D171" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E171" s="21"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A172" s="21"/>
-      <c r="B172" s="20"/>
-      <c r="C172" s="20"/>
-      <c r="D172" s="7" t="s">
+    <row r="172" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A172" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A173" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E172" s="21"/>
-    </row>
-    <row r="173" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A173" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D173" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A174" s="5" t="s">
+      <c r="B173" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D173" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B174" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C174" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="D174" s="7" t="s">
+      <c r="E173" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A175" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="E174" s="5" t="s">
-        <v>286</v>
-      </c>
+      <c r="B175" s="20"/>
+      <c r="C175" s="20"/>
+      <c r="D175" s="20"/>
+      <c r="E175" s="20"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A176" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="B176" s="20"/>
-      <c r="C176" s="20"/>
-      <c r="D176" s="20"/>
-      <c r="E176" s="20"/>
+      <c r="A176" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B176" s="19"/>
+      <c r="C176" s="19"/>
+      <c r="D176" s="19"/>
+      <c r="E176" s="19"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A177" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="B177" s="24"/>
-      <c r="C177" s="24"/>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A178" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="B178" s="20"/>
-      <c r="C178" s="20"/>
-      <c r="D178" s="20"/>
-      <c r="E178" s="20"/>
+      <c r="A177" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="B177" s="20"/>
+      <c r="C177" s="20"/>
+      <c r="D177" s="20"/>
+      <c r="E177" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="170">
-    <mergeCell ref="A177:E177"/>
-    <mergeCell ref="A178:E178"/>
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="E167:E172"/>
-    <mergeCell ref="C167:C172"/>
-    <mergeCell ref="B167:B172"/>
-    <mergeCell ref="A167:A172"/>
-    <mergeCell ref="C156:C164"/>
-    <mergeCell ref="B156:B164"/>
-    <mergeCell ref="A156:A164"/>
-    <mergeCell ref="E156:E164"/>
-    <mergeCell ref="E165:E166"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="E145:E151"/>
-    <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B145:B151"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="A135:A140"/>
-    <mergeCell ref="B135:B140"/>
-    <mergeCell ref="C135:C140"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="E138:E140"/>
-    <mergeCell ref="E135:E137"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="E133:E134"/>
-    <mergeCell ref="B125:B130"/>
-    <mergeCell ref="C125:C130"/>
-    <mergeCell ref="A125:A130"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="E131:E132"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="E128:E130"/>
-    <mergeCell ref="E125:E127"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="C117:C122"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="A117:A122"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="E106:E111"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="A99:A105"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="E99:E105"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="E93:E95"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B19"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="C13:C19"/>
+    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A62:A71"/>
     <mergeCell ref="B62:B71"/>
     <mergeCell ref="C62:C71"/>
@@ -3498,42 +3412,116 @@
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A55:A59"/>
     <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="A99:A105"/>
+    <mergeCell ref="B99:B105"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="E99:E105"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="E85:E87"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="C117:C122"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="A117:A122"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="E106:E111"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="E133:E134"/>
+    <mergeCell ref="B125:B130"/>
+    <mergeCell ref="C125:C130"/>
+    <mergeCell ref="A125:A130"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="E131:E132"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="E128:E130"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="B135:B140"/>
+    <mergeCell ref="C135:C140"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="E138:E140"/>
+    <mergeCell ref="E135:E137"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="E145:E151"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B145:B151"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="E166:E171"/>
+    <mergeCell ref="C166:C171"/>
+    <mergeCell ref="B166:B171"/>
+    <mergeCell ref="A166:A171"/>
+    <mergeCell ref="C156:C163"/>
+    <mergeCell ref="B156:B163"/>
+    <mergeCell ref="A156:A163"/>
+    <mergeCell ref="E156:E163"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A164:A165"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFAC421-495E-4534-B554-6B0F8C05B6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C295FE-25E0-424C-AC68-AFF2707193CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -1014,7 +1014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1034,9 +1034,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1403,1891 +1400,1891 @@
   <cols>
     <col min="1" max="1" width="12.31640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.31640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="40.54296875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="40.54296875" style="10" customWidth="1"/>
     <col min="4" max="4" width="50.6796875" style="4" customWidth="1"/>
     <col min="5" max="5" width="25.36328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A3" s="21"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="24"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A4" s="21"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="24"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="21"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A5" s="21"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="24"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="21"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A6" s="21"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="24"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="22"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="9" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="22"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="9" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" ht="24.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="23" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="21"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="24"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A12" s="21"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" s="22"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="9" t="s">
+      <c r="A14" s="21"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" s="22"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="9" t="s">
+      <c r="A15" s="21"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" s="22"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="9" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" s="22"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="9" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" s="22"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="9" t="s">
+      <c r="A18" s="21"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="22"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" s="22"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="9" t="s">
+      <c r="A19" s="21"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="22"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A21" s="21"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="24"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
       <c r="D21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="21"/>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A23" s="22"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="9" t="s">
+      <c r="A23" s="21"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="22"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A24" s="22"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="9" t="s">
+      <c r="A24" s="21"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="22"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A25" s="22"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="9" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="22"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A26" s="22"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="9" t="s">
+      <c r="A26" s="21"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="22"/>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A27" s="22"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="9" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="22"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A28" s="22"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="9" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="22"/>
+      <c r="E28" s="21"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A29" s="22"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="9" t="s">
+      <c r="A29" s="21"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="22"/>
+      <c r="E29" s="21"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A30" s="22"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="9" t="s">
+      <c r="A30" s="21"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="22"/>
+      <c r="E30" s="21"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="19" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A32" s="21"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
       <c r="D32" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="21"/>
+      <c r="E32" s="20"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A33" s="21"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
       <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="21"/>
+      <c r="E33" s="20"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A34" s="21"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="21"/>
+      <c r="E34" s="20"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A35" s="21"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
       <c r="D35" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E35" s="21"/>
+      <c r="E35" s="20"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A37" s="22"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="9" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="22"/>
+      <c r="E37" s="21"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A38" s="22"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="9" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="22"/>
+      <c r="E38" s="21"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="19" t="s">
         <v>62</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A40" s="21"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
       <c r="D40" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="21"/>
+      <c r="E40" s="20"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A41" s="21"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="21"/>
+      <c r="E41" s="20"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A42" s="21"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
       <c r="D42" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="20"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A43" s="21"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
       <c r="D43" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="21"/>
+      <c r="E43" s="20"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="E44" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="9" t="s">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="22"/>
+      <c r="E45" s="21"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="9" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="22"/>
+      <c r="E46" s="21"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A48" s="21"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="24"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="23"/>
       <c r="D48" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="21"/>
-    </row>
-    <row r="49" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="22" t="s">
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A49" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="22"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="9" t="s">
+      <c r="E49" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A50" s="21"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="22"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="19" t="s">
         <v>69</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A52" s="21"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
       <c r="D52" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="20"/>
     </row>
     <row r="53" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="21"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
       <c r="D53" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E53" s="21"/>
+      <c r="E53" s="20"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A54" s="21"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
       <c r="D54" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="21"/>
-    </row>
-    <row r="55" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="22" t="s">
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A55" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="22"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="9" t="s">
+      <c r="E55" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A56" s="21"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E56" s="22"/>
-    </row>
-    <row r="57" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="22"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="9" t="s">
+      <c r="E56" s="21"/>
+    </row>
+    <row r="57" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A57" s="21"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="22"/>
-    </row>
-    <row r="58" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="22"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="9" t="s">
+      <c r="E57" s="21"/>
+    </row>
+    <row r="58" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A58" s="21"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="22"/>
-    </row>
-    <row r="59" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="22"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="9" t="s">
+      <c r="E58" s="21"/>
+    </row>
+    <row r="59" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A59" s="21"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="22"/>
+      <c r="E59" s="21"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="C60" s="23" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="21" t="s">
+      <c r="E60" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A61" s="21"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="24"/>
+      <c r="A61" s="20"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="23"/>
       <c r="D61" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="21"/>
+      <c r="E61" s="20"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A63" s="22"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="9" t="s">
+      <c r="A63" s="21"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E63" s="22"/>
+      <c r="E63" s="21"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A64" s="22"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="9" t="s">
+      <c r="A64" s="21"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="22"/>
+      <c r="E64" s="21"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A65" s="22"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="9" t="s">
+      <c r="A65" s="21"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="22"/>
+      <c r="E65" s="21"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A66" s="22"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="9" t="s">
+      <c r="A66" s="21"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="22"/>
+      <c r="E66" s="21"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A67" s="22"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="9" t="s">
+      <c r="A67" s="21"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="22"/>
+      <c r="E67" s="21"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A68" s="22"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="9" t="s">
+      <c r="A68" s="21"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="22"/>
+      <c r="E68" s="21"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A69" s="22"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="9" t="s">
+      <c r="A69" s="21"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="22"/>
+      <c r="E69" s="21"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A70" s="22"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="9" t="s">
+      <c r="A70" s="21"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="22"/>
+      <c r="E70" s="21"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A71" s="22"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="9" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="22"/>
+      <c r="E71" s="21"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="19" t="s">
         <v>102</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E72" s="21" t="s">
+      <c r="E72" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A73" s="21"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
+      <c r="A73" s="20"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
       <c r="D73" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E73" s="21"/>
+      <c r="E73" s="20"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A74" s="21"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
+      <c r="A74" s="20"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
       <c r="D74" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E74" s="21"/>
+      <c r="E74" s="20"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A75" s="21"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
+      <c r="A75" s="20"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
       <c r="D75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E75" s="21"/>
+      <c r="E75" s="20"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A76" s="21"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
       <c r="D76" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E76" s="21"/>
+      <c r="E76" s="20"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A77" s="22" t="s">
+      <c r="A77" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="19" t="s">
+      <c r="B77" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D77" s="9" t="s">
+      <c r="D77" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A78" s="22"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="9" t="s">
+      <c r="A78" s="21"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="22"/>
+      <c r="E78" s="21"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A79" s="22"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="9" t="s">
+      <c r="A79" s="21"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="22"/>
+      <c r="E79" s="21"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="19" t="s">
         <v>104</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E80" s="21" t="s">
+      <c r="E80" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A81" s="21"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
+      <c r="A81" s="20"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
       <c r="D81" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E81" s="21"/>
+      <c r="E81" s="20"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A82" s="21"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
       <c r="D82" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E82" s="21"/>
+      <c r="E82" s="20"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A83" s="21"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="20"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
       <c r="D83" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="20"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A84" s="21"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
       <c r="D84" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E84" s="21"/>
+      <c r="E84" s="20"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A85" s="22" t="s">
+      <c r="A85" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B85" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E85" s="22" t="s">
+      <c r="E85" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A86" s="22"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="9" t="s">
+      <c r="A86" s="21"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E86" s="22"/>
+      <c r="E86" s="21"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A87" s="22"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="9" t="s">
+      <c r="A87" s="21"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="E87" s="22"/>
+      <c r="E87" s="21"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A88" s="21" t="s">
+      <c r="A88" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B88" s="20" t="s">
+      <c r="B88" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="24" t="s">
+      <c r="C88" s="23" t="s">
         <v>32</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="21" t="s">
+      <c r="E88" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A89" s="21"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="24"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="23"/>
       <c r="D89" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="21"/>
+      <c r="E89" s="20"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A90" s="22" t="s">
+      <c r="A90" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="19" t="s">
+      <c r="B90" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D90" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="22" t="s">
+      <c r="E90" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A91" s="22"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="9" t="s">
+      <c r="A91" s="21"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="22"/>
+      <c r="E91" s="21"/>
     </row>
     <row r="92" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="22"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="9" t="s">
+      <c r="A92" s="21"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E92" s="22"/>
+      <c r="E92" s="21"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A93" s="21" t="s">
+      <c r="A93" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B93" s="20" t="s">
+      <c r="B93" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="24" t="s">
+      <c r="C93" s="23" t="s">
         <v>122</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E93" s="21" t="s">
+      <c r="E93" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A94" s="21"/>
-      <c r="B94" s="20"/>
-      <c r="C94" s="24"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="23"/>
       <c r="D94" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E94" s="21"/>
+      <c r="E94" s="20"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A95" s="21"/>
-      <c r="B95" s="20"/>
-      <c r="C95" s="24"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="23"/>
       <c r="D95" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E95" s="21"/>
+      <c r="E95" s="20"/>
     </row>
     <row r="96" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="22" t="s">
+      <c r="A96" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D96" s="9" t="s">
+      <c r="D96" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="22" t="s">
+      <c r="E96" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="22"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="9" t="s">
+      <c r="A97" s="21"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E97" s="22"/>
+      <c r="E97" s="21"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A98" s="22"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="9" t="s">
+      <c r="A98" s="21"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="E98" s="22"/>
+      <c r="E98" s="21"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A99" s="21" t="s">
+      <c r="A99" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B99" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="24" t="s">
+      <c r="C99" s="23" t="s">
         <v>213</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E99" s="21" t="s">
+      <c r="E99" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="24"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="23"/>
       <c r="D100" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E100" s="21"/>
+      <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A101" s="21"/>
-      <c r="B101" s="20"/>
-      <c r="C101" s="24"/>
+      <c r="A101" s="20"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="23"/>
       <c r="D101" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="E101" s="21"/>
+      <c r="E101" s="20"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A102" s="21"/>
-      <c r="B102" s="20"/>
-      <c r="C102" s="24"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="23"/>
       <c r="D102" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E102" s="21"/>
+      <c r="E102" s="20"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A103" s="21"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="24"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="23"/>
       <c r="D103" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E103" s="21"/>
+      <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A104" s="21"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="24"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="23"/>
       <c r="D104" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E104" s="21"/>
+      <c r="E104" s="20"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A105" s="21"/>
-      <c r="B105" s="20"/>
-      <c r="C105" s="24"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="23"/>
       <c r="D105" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E105" s="21"/>
+      <c r="E105" s="20"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A106" s="22" t="s">
+      <c r="A106" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="19" t="s">
+      <c r="B106" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="19" t="s">
+      <c r="C106" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D106" s="9" t="s">
+      <c r="D106" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="22" t="s">
+      <c r="E106" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A107" s="22"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-      <c r="D107" s="9" t="s">
+      <c r="A107" s="21"/>
+      <c r="B107" s="18"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="22"/>
+      <c r="E107" s="21"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A108" s="22"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-      <c r="D108" s="9" t="s">
+      <c r="A108" s="21"/>
+      <c r="B108" s="18"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="22"/>
+      <c r="E108" s="21"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A109" s="22"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-      <c r="D109" s="9" t="s">
+      <c r="A109" s="21"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E109" s="22"/>
+      <c r="E109" s="21"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A110" s="22"/>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-      <c r="D110" s="9" t="s">
+      <c r="A110" s="21"/>
+      <c r="B110" s="18"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E110" s="22"/>
+      <c r="E110" s="21"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A111" s="22"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="9" t="s">
+      <c r="A111" s="21"/>
+      <c r="B111" s="18"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="22"/>
+      <c r="E111" s="21"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C112" s="20" t="s">
+      <c r="C112" s="19" t="s">
         <v>169</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E112" s="21" t="s">
+      <c r="E112" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A113" s="21"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="20"/>
+      <c r="A113" s="20"/>
+      <c r="B113" s="19"/>
+      <c r="C113" s="19"/>
       <c r="D113" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E113" s="21"/>
+      <c r="E113" s="20"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A114" s="21"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="20"/>
+      <c r="A114" s="20"/>
+      <c r="B114" s="19"/>
+      <c r="C114" s="19"/>
       <c r="D114" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E114" s="21"/>
+      <c r="E114" s="20"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A115" s="21"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="20"/>
+      <c r="A115" s="20"/>
+      <c r="B115" s="19"/>
+      <c r="C115" s="19"/>
       <c r="D115" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E115" s="21"/>
+      <c r="E115" s="20"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A116" s="21"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="20"/>
+      <c r="A116" s="20"/>
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
       <c r="D116" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E116" s="21"/>
+      <c r="E116" s="20"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A117" s="22" t="s">
+      <c r="A117" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="D117" s="9" t="s">
+      <c r="D117" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="22" t="s">
+      <c r="E117" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A118" s="22"/>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-      <c r="D118" s="9" t="s">
+      <c r="A118" s="21"/>
+      <c r="B118" s="18"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="22"/>
+      <c r="E118" s="21"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A119" s="22"/>
-      <c r="B119" s="19"/>
-      <c r="C119" s="19"/>
-      <c r="D119" s="9" t="s">
+      <c r="A119" s="21"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E119" s="8"/>
+      <c r="E119" s="21"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A120" s="22"/>
-      <c r="B120" s="19"/>
-      <c r="C120" s="19"/>
-      <c r="D120" s="9" t="s">
+      <c r="A120" s="21"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E120" s="22" t="s">
+      <c r="E120" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A121" s="22"/>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-      <c r="D121" s="9" t="s">
+      <c r="A121" s="21"/>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E121" s="22"/>
+      <c r="E121" s="21"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A122" s="22"/>
-      <c r="B122" s="19"/>
-      <c r="C122" s="19"/>
-      <c r="D122" s="9" t="s">
+      <c r="A122" s="21"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="E122" s="22"/>
+      <c r="E122" s="21"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B123" s="20" t="s">
+      <c r="B123" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C123" s="20" t="s">
+      <c r="C123" s="19" t="s">
         <v>184</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E123" s="21" t="s">
+      <c r="E123" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A124" s="21"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
+      <c r="A124" s="20"/>
+      <c r="B124" s="19"/>
+      <c r="C124" s="19"/>
       <c r="D124" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E124" s="21"/>
+      <c r="E124" s="20"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="B125" s="19" t="s">
+      <c r="B125" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="D125" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E125" s="22" t="s">
+      <c r="E125" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A126" s="22"/>
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-      <c r="D126" s="9" t="s">
+      <c r="A126" s="21"/>
+      <c r="B126" s="18"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E126" s="22"/>
+      <c r="E126" s="21"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A127" s="22"/>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="9" t="s">
+      <c r="A127" s="21"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E127" s="22"/>
+      <c r="E127" s="21" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A128" s="22"/>
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="9" t="s">
+      <c r="A128" s="21"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E128" s="22" t="s">
-        <v>29</v>
-      </c>
+      <c r="E128" s="21"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A129" s="22"/>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="9" t="s">
+      <c r="A129" s="21"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="E129" s="22"/>
+      <c r="E129" s="21"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A130" s="22"/>
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-      <c r="D130" s="9" t="s">
+      <c r="A130" s="21"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E130" s="22"/>
+      <c r="E130" s="21"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A131" s="21" t="s">
+      <c r="A131" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B131" s="20" t="s">
+      <c r="B131" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="24" t="s">
+      <c r="C131" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E131" s="21" t="s">
+      <c r="E131" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A132" s="21"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="24"/>
+      <c r="A132" s="20"/>
+      <c r="B132" s="19"/>
+      <c r="C132" s="23"/>
       <c r="D132" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E132" s="21"/>
+      <c r="E132" s="20"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A133" s="22" t="s">
+      <c r="A133" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B133" s="19" t="s">
+      <c r="B133" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="19" t="s">
+      <c r="C133" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D133" s="9" t="s">
+      <c r="D133" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E133" s="22" t="s">
+      <c r="E133" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A134" s="22"/>
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
-      <c r="D134" s="9" t="s">
+      <c r="A134" s="21"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E134" s="22"/>
+      <c r="E134" s="21"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A135" s="21" t="s">
+      <c r="A135" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="B135" s="20" t="s">
+      <c r="B135" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C135" s="20" t="s">
+      <c r="C135" s="19" t="s">
         <v>193</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="E135" s="21" t="s">
+      <c r="E135" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A136" s="21"/>
-      <c r="B136" s="20"/>
-      <c r="C136" s="20"/>
+      <c r="A136" s="20"/>
+      <c r="B136" s="19"/>
+      <c r="C136" s="19"/>
       <c r="D136" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E136" s="21"/>
+      <c r="E136" s="20"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A137" s="21"/>
-      <c r="B137" s="20"/>
-      <c r="C137" s="20"/>
+      <c r="A137" s="20"/>
+      <c r="B137" s="19"/>
+      <c r="C137" s="19"/>
       <c r="D137" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="E137" s="21"/>
+      <c r="E137" s="20" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A138" s="21"/>
-      <c r="B138" s="20"/>
-      <c r="C138" s="20"/>
+      <c r="A138" s="20"/>
+      <c r="B138" s="19"/>
+      <c r="C138" s="19"/>
       <c r="D138" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E138" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="E138" s="20"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A139" s="21"/>
-      <c r="B139" s="20"/>
-      <c r="C139" s="20"/>
+      <c r="A139" s="20"/>
+      <c r="B139" s="19"/>
+      <c r="C139" s="19"/>
       <c r="D139" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E139" s="21"/>
+      <c r="E139" s="20"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A140" s="21"/>
-      <c r="B140" s="20"/>
-      <c r="C140" s="20"/>
+      <c r="A140" s="20"/>
+      <c r="B140" s="19"/>
+      <c r="C140" s="19"/>
       <c r="D140" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E140" s="21"/>
+      <c r="E140" s="20"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A141" s="22" t="s">
+      <c r="A141" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="B141" s="19" t="s">
+      <c r="B141" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C141" s="23" t="s">
+      <c r="C141" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D141" s="9" t="s">
+      <c r="D141" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E141" s="22" t="s">
+      <c r="E141" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A142" s="22"/>
-      <c r="B142" s="19"/>
-      <c r="C142" s="23"/>
-      <c r="D142" s="9" t="s">
+      <c r="A142" s="21"/>
+      <c r="B142" s="18"/>
+      <c r="C142" s="22"/>
+      <c r="D142" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E142" s="22"/>
+      <c r="E142" s="21"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A143" s="21" t="s">
+      <c r="A143" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B143" s="20" t="s">
+      <c r="B143" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C143" s="20" t="s">
+      <c r="C143" s="19" t="s">
         <v>184</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E143" s="21" t="s">
+      <c r="E143" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A144" s="21"/>
-      <c r="B144" s="20"/>
-      <c r="C144" s="20"/>
+      <c r="A144" s="20"/>
+      <c r="B144" s="19"/>
+      <c r="C144" s="19"/>
       <c r="D144" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E144" s="21"/>
+      <c r="E144" s="20"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A145" s="22" t="s">
+      <c r="A145" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="B145" s="19" t="s">
+      <c r="B145" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C145" s="19" t="s">
+      <c r="C145" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="D145" s="9" t="s">
+      <c r="D145" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E145" s="22" t="s">
+      <c r="E145" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A146" s="22"/>
-      <c r="B146" s="19"/>
-      <c r="C146" s="19"/>
-      <c r="D146" s="9" t="s">
+      <c r="A146" s="21"/>
+      <c r="B146" s="18"/>
+      <c r="C146" s="18"/>
+      <c r="D146" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E146" s="22"/>
+      <c r="E146" s="21"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A147" s="22"/>
-      <c r="B147" s="19"/>
-      <c r="C147" s="19"/>
-      <c r="D147" s="9" t="s">
+      <c r="A147" s="21"/>
+      <c r="B147" s="18"/>
+      <c r="C147" s="18"/>
+      <c r="D147" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E147" s="22"/>
+      <c r="E147" s="21"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A148" s="22"/>
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
-      <c r="D148" s="9" t="s">
+      <c r="A148" s="21"/>
+      <c r="B148" s="18"/>
+      <c r="C148" s="18"/>
+      <c r="D148" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E148" s="22"/>
+      <c r="E148" s="21"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A149" s="22"/>
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-      <c r="D149" s="9" t="s">
+      <c r="A149" s="21"/>
+      <c r="B149" s="18"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E149" s="22"/>
+      <c r="E149" s="21"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A150" s="22"/>
-      <c r="B150" s="19"/>
-      <c r="C150" s="19"/>
-      <c r="D150" s="9" t="s">
+      <c r="A150" s="21"/>
+      <c r="B150" s="18"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E150" s="22"/>
+      <c r="E150" s="21"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A151" s="22"/>
-      <c r="B151" s="19"/>
-      <c r="C151" s="19"/>
-      <c r="D151" s="9" t="s">
+      <c r="A151" s="21"/>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E151" s="22"/>
+      <c r="E151" s="21"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A152" s="21" t="s">
+      <c r="A152" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="B152" s="20" t="s">
+      <c r="B152" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C152" s="20" t="s">
+      <c r="C152" s="19" t="s">
         <v>212</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E152" s="21" t="s">
+      <c r="E152" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A153" s="21"/>
-      <c r="B153" s="20"/>
-      <c r="C153" s="20"/>
+      <c r="A153" s="20"/>
+      <c r="B153" s="19"/>
+      <c r="C153" s="19"/>
       <c r="D153" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="E153" s="21"/>
+      <c r="E153" s="20"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A154" s="22" t="s">
+      <c r="A154" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="B154" s="19" t="s">
+      <c r="B154" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C154" s="19" t="s">
+      <c r="C154" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="D154" s="9" t="s">
+      <c r="D154" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E154" s="22" t="s">
+      <c r="E154" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A155" s="22"/>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
-      <c r="D155" s="9" t="s">
+      <c r="A155" s="21"/>
+      <c r="B155" s="18"/>
+      <c r="C155" s="18"/>
+      <c r="D155" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E155" s="22"/>
+      <c r="E155" s="21"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="B156" s="20" t="s">
+      <c r="B156" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="C156" s="20" t="s">
+      <c r="C156" s="19" t="s">
         <v>229</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E156" s="21" t="s">
+      <c r="E156" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A157" s="21"/>
-      <c r="B157" s="20"/>
-      <c r="C157" s="20"/>
+      <c r="A157" s="20"/>
+      <c r="B157" s="19"/>
+      <c r="C157" s="19"/>
       <c r="D157" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="E157" s="21"/>
+      <c r="E157" s="20"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A158" s="21"/>
-      <c r="B158" s="20"/>
-      <c r="C158" s="20"/>
+      <c r="A158" s="20"/>
+      <c r="B158" s="19"/>
+      <c r="C158" s="19"/>
       <c r="D158" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="E158" s="21"/>
+      <c r="E158" s="20"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A159" s="21"/>
-      <c r="B159" s="20"/>
-      <c r="C159" s="20"/>
+      <c r="A159" s="20"/>
+      <c r="B159" s="19"/>
+      <c r="C159" s="19"/>
       <c r="D159" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E159" s="21"/>
+      <c r="E159" s="20"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A160" s="21"/>
-      <c r="B160" s="20"/>
-      <c r="C160" s="20"/>
+      <c r="A160" s="20"/>
+      <c r="B160" s="19"/>
+      <c r="C160" s="19"/>
       <c r="D160" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="E160" s="21"/>
+      <c r="E160" s="20"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A161" s="21"/>
-      <c r="B161" s="20"/>
-      <c r="C161" s="20"/>
+      <c r="A161" s="20"/>
+      <c r="B161" s="19"/>
+      <c r="C161" s="19"/>
       <c r="D161" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E161" s="21"/>
+      <c r="E161" s="20"/>
     </row>
     <row r="162" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A162" s="21"/>
-      <c r="B162" s="20"/>
-      <c r="C162" s="20"/>
-      <c r="D162" s="18" t="s">
+      <c r="A162" s="20"/>
+      <c r="B162" s="19"/>
+      <c r="C162" s="19"/>
+      <c r="D162" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="E162" s="21"/>
+      <c r="E162" s="20"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A163" s="21"/>
-      <c r="B163" s="20"/>
-      <c r="C163" s="20"/>
+      <c r="A163" s="20"/>
+      <c r="B163" s="19"/>
+      <c r="C163" s="19"/>
       <c r="D163" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E163" s="21"/>
+      <c r="E163" s="20"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A164" s="22" t="s">
+      <c r="A164" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B164" s="19" t="s">
+      <c r="B164" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C164" s="19" t="s">
+      <c r="C164" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="D164" s="9" t="s">
+      <c r="D164" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E164" s="22" t="s">
+      <c r="E164" s="21" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A165" s="22"/>
-      <c r="B165" s="19"/>
-      <c r="C165" s="19"/>
-      <c r="D165" s="9" t="s">
+      <c r="A165" s="21"/>
+      <c r="B165" s="18"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E165" s="22"/>
+      <c r="E165" s="21"/>
     </row>
     <row r="166" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A166" s="21" t="s">
+      <c r="A166" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="B166" s="20" t="s">
+      <c r="B166" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="C166" s="20" t="s">
+      <c r="C166" s="19" t="s">
         <v>239</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E166" s="21" t="s">
+      <c r="E166" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A167" s="21"/>
-      <c r="B167" s="20"/>
-      <c r="C167" s="20"/>
+      <c r="A167" s="20"/>
+      <c r="B167" s="19"/>
+      <c r="C167" s="19"/>
       <c r="D167" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E167" s="21"/>
+      <c r="E167" s="20"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A168" s="21"/>
-      <c r="B168" s="20"/>
-      <c r="C168" s="20"/>
+      <c r="A168" s="20"/>
+      <c r="B168" s="19"/>
+      <c r="C168" s="19"/>
       <c r="D168" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E168" s="21"/>
+      <c r="E168" s="20"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A169" s="21"/>
-      <c r="B169" s="20"/>
-      <c r="C169" s="20"/>
+      <c r="A169" s="20"/>
+      <c r="B169" s="19"/>
+      <c r="C169" s="19"/>
       <c r="D169" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="E169" s="21"/>
+      <c r="E169" s="20"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A170" s="21"/>
-      <c r="B170" s="20"/>
-      <c r="C170" s="20"/>
+      <c r="A170" s="20"/>
+      <c r="B170" s="19"/>
+      <c r="C170" s="19"/>
       <c r="D170" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E170" s="21"/>
+      <c r="E170" s="20"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A171" s="21"/>
-      <c r="B171" s="20"/>
-      <c r="C171" s="20"/>
+      <c r="A171" s="20"/>
+      <c r="B171" s="19"/>
+      <c r="C171" s="19"/>
       <c r="D171" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E171" s="21"/>
+      <c r="E171" s="20"/>
     </row>
     <row r="172" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A172" s="2" t="s">
@@ -3296,7 +3293,7 @@
       <c r="B172" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C172" s="11" t="s">
+      <c r="C172" s="10" t="s">
         <v>260</v>
       </c>
       <c r="D172" s="4" t="s">
@@ -3313,7 +3310,7 @@
       <c r="B173" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C173" s="9" t="s">
         <v>268</v>
       </c>
       <c r="D173" s="7" t="s">
@@ -3324,31 +3321,31 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A175" s="20" t="s">
+      <c r="A175" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="B175" s="20"/>
-      <c r="C175" s="20"/>
-      <c r="D175" s="20"/>
-      <c r="E175" s="20"/>
+      <c r="B175" s="19"/>
+      <c r="C175" s="19"/>
+      <c r="D175" s="19"/>
+      <c r="E175" s="19"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A176" s="19" t="s">
+      <c r="A176" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="B176" s="19"/>
-      <c r="C176" s="19"/>
-      <c r="D176" s="19"/>
-      <c r="E176" s="19"/>
+      <c r="B176" s="18"/>
+      <c r="C176" s="18"/>
+      <c r="D176" s="18"/>
+      <c r="E176" s="18"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A177" s="20" t="s">
+      <c r="A177" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="B177" s="20"/>
-      <c r="C177" s="20"/>
-      <c r="D177" s="20"/>
-      <c r="E177" s="20"/>
+      <c r="B177" s="19"/>
+      <c r="C177" s="19"/>
+      <c r="D177" s="19"/>
+      <c r="E177" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="170">
@@ -3457,14 +3454,14 @@
     <mergeCell ref="C117:C122"/>
     <mergeCell ref="B117:B122"/>
     <mergeCell ref="A117:A122"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E120:E122"/>
     <mergeCell ref="C106:C111"/>
     <mergeCell ref="B106:B111"/>
     <mergeCell ref="A106:A111"/>
     <mergeCell ref="E106:E111"/>
     <mergeCell ref="E112:E116"/>
     <mergeCell ref="C112:C116"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="E117:E119"/>
     <mergeCell ref="C123:C124"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="A123:A124"/>
@@ -3480,8 +3477,8 @@
     <mergeCell ref="C131:C132"/>
     <mergeCell ref="E131:E132"/>
     <mergeCell ref="A131:A132"/>
-    <mergeCell ref="E128:E130"/>
-    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="E125:E126"/>
+    <mergeCell ref="E127:E130"/>
     <mergeCell ref="A135:A140"/>
     <mergeCell ref="B135:B140"/>
     <mergeCell ref="C135:C140"/>
@@ -3493,8 +3490,8 @@
     <mergeCell ref="E152:E153"/>
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="A152:A153"/>
-    <mergeCell ref="E138:E140"/>
-    <mergeCell ref="E135:E137"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="E137:E140"/>
     <mergeCell ref="B154:B155"/>
     <mergeCell ref="C154:C155"/>
     <mergeCell ref="A154:A155"/>

--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C295FE-25E0-424C-AC68-AFF2707193CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9002513-0082-41F2-B75F-DFCBFA9FA49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="288">
   <si>
     <t>Feature ID</t>
   </si>
@@ -1014,7 +1014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1064,7 +1064,10 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1073,13 +1076,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1423,63 +1426,63 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A3" s="20"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="23"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="21"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A4" s="20"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="23"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A5" s="20"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A6" s="20"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="22" t="s">
@@ -1488,68 +1491,68 @@
       <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="21"/>
-      <c r="B8" s="18"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="22"/>
       <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="21"/>
-      <c r="B9" s="18"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="22"/>
       <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" ht="24.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="19" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="E11" s="20"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E12" s="20"/>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="24" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="22" t="s">
@@ -1558,835 +1561,835 @@
       <c r="D13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" s="21"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="22"/>
       <c r="D14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="23"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" s="21"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="22"/>
       <c r="D15" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" s="21"/>
-      <c r="B16" s="18"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="22"/>
       <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" s="21"/>
-      <c r="B17" s="18"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="22"/>
       <c r="D17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" s="21"/>
-      <c r="B18" s="18"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="22"/>
       <c r="D18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" s="21"/>
-      <c r="B19" s="18"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="22"/>
       <c r="D19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A21" s="20"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="23"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="24" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A23" s="21"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
       <c r="D23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="21"/>
+      <c r="E23" s="23"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A24" s="21"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="21"/>
+      <c r="E24" s="23"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A25" s="21"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="21"/>
+      <c r="E25" s="23"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A26" s="21"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="21"/>
+      <c r="E26" s="23"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A27" s="21"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
       <c r="D27" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="21"/>
+      <c r="E27" s="23"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A28" s="21"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="21"/>
+      <c r="E28" s="23"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A29" s="21"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
       <c r="D29" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="21"/>
+      <c r="E29" s="23"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A30" s="21"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="21"/>
+      <c r="E30" s="23"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A32" s="20"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="20"/>
+      <c r="E32" s="21"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A33" s="20"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
       <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="20"/>
+      <c r="E33" s="21"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A34" s="20"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="20"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A35" s="20"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E35" s="20"/>
+      <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="24" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A37" s="21"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
       <c r="D37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="21"/>
+      <c r="E37" s="23"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A38" s="21"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
       <c r="D38" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="21"/>
+      <c r="E38" s="23"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A40" s="20"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="20"/>
+      <c r="E40" s="21"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A41" s="20"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="20"/>
+      <c r="E41" s="21"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A42" s="20"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
       <c r="D42" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="20"/>
+      <c r="E42" s="21"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A43" s="20"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
       <c r="D43" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="20"/>
+      <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="24" t="s">
         <v>108</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="E44" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="18"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="24"/>
       <c r="D45" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="21"/>
+      <c r="E45" s="23"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="18"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24"/>
       <c r="D46" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="21"/>
+      <c r="E46" s="23"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A48" s="20"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="23"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="19"/>
       <c r="D48" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="20"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="24" t="s">
         <v>81</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="E49" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="21"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="21"/>
+      <c r="E50" s="23"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="20" t="s">
         <v>69</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A52" s="20"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="E52" s="20"/>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="20"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E53" s="20"/>
+      <c r="E53" s="21"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A54" s="20"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
       <c r="D54" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="20"/>
+      <c r="E54" s="21"/>
     </row>
     <row r="55" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="24" t="s">
         <v>72</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="21"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="23"/>
     </row>
     <row r="57" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="21"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="21"/>
+      <c r="E57" s="23"/>
     </row>
     <row r="58" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="21"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="21"/>
+      <c r="E58" s="23"/>
     </row>
     <row r="59" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="21"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="21"/>
+      <c r="E59" s="23"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="19" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A61" s="20"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="23"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="19"/>
       <c r="D61" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="20"/>
+      <c r="E61" s="21"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="24" t="s">
         <v>98</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A63" s="21"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E63" s="21"/>
+      <c r="E63" s="23"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A64" s="21"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="21"/>
+      <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A65" s="21"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="21"/>
+      <c r="E65" s="23"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A66" s="21"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="21"/>
+      <c r="E66" s="23"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A67" s="21"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="21"/>
+      <c r="E67" s="23"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A68" s="21"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="21"/>
+      <c r="E68" s="23"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A69" s="21"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="21"/>
+      <c r="E69" s="23"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A70" s="21"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="21"/>
+      <c r="E70" s="23"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A71" s="21"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="21"/>
+      <c r="E71" s="23"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="20" t="s">
         <v>102</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A73" s="20"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
+      <c r="A73" s="21"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
       <c r="D73" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E73" s="20"/>
+      <c r="E73" s="21"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A74" s="20"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
+      <c r="A74" s="21"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E74" s="20"/>
+      <c r="E74" s="21"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A75" s="20"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
+      <c r="A75" s="21"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
       <c r="D75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E75" s="20"/>
+      <c r="E75" s="21"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A76" s="20"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
+      <c r="A76" s="21"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E76" s="20"/>
+      <c r="E76" s="21"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A77" s="21" t="s">
+      <c r="A77" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="24" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="21" t="s">
+      <c r="E77" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A78" s="21"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="23"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A79" s="21"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
+      <c r="A79" s="23"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="21"/>
+      <c r="E79" s="23"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="19" t="s">
+      <c r="B80" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E80" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A81" s="20"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
+      <c r="A81" s="21"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E81" s="20"/>
+      <c r="E81" s="21"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A82" s="20"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
+      <c r="A82" s="21"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E82" s="20"/>
+      <c r="E82" s="21"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A83" s="20"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
+      <c r="A83" s="21"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
       <c r="D83" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E83" s="20"/>
+      <c r="E83" s="21"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A84" s="20"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
+      <c r="A84" s="21"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E84" s="20"/>
+      <c r="E84" s="21"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A85" s="21" t="s">
+      <c r="A85" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="24" t="s">
         <v>107</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E85" s="21" t="s">
+      <c r="E85" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A86" s="21"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
+      <c r="A86" s="23"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="24"/>
       <c r="D86" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E86" s="21"/>
+      <c r="E86" s="23"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A87" s="21"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
+      <c r="A87" s="23"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
       <c r="D87" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="E87" s="21"/>
+      <c r="E87" s="23"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A88" s="20" t="s">
+      <c r="A88" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="19" t="s">
         <v>32</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="20" t="s">
+      <c r="E88" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A89" s="20"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="23"/>
+      <c r="A89" s="21"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="19"/>
       <c r="D89" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="20"/>
+      <c r="E89" s="21"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="24" t="s">
         <v>39</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -2395,68 +2398,68 @@
       <c r="D90" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="21" t="s">
+      <c r="E90" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A91" s="21"/>
-      <c r="B91" s="18"/>
+      <c r="A91" s="23"/>
+      <c r="B91" s="24"/>
       <c r="C91" s="22"/>
       <c r="D91" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="21"/>
+      <c r="E91" s="23"/>
     </row>
     <row r="92" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="21"/>
-      <c r="B92" s="18"/>
+      <c r="A92" s="23"/>
+      <c r="B92" s="24"/>
       <c r="C92" s="22"/>
       <c r="D92" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E92" s="21"/>
+      <c r="E92" s="23"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A93" s="20" t="s">
+      <c r="A93" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B93" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="19" t="s">
         <v>122</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E93" s="20" t="s">
+      <c r="E93" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A94" s="20"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="23"/>
+      <c r="A94" s="21"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="19"/>
       <c r="D94" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E94" s="20"/>
+      <c r="E94" s="21"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A95" s="20"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="23"/>
+      <c r="A95" s="21"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="19"/>
       <c r="D95" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E95" s="20"/>
+      <c r="E95" s="21"/>
     </row>
     <row r="96" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="21" t="s">
+      <c r="A96" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -2465,489 +2468,493 @@
       <c r="D96" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="21" t="s">
+      <c r="E96" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="21"/>
-      <c r="B97" s="18"/>
+      <c r="A97" s="23"/>
+      <c r="B97" s="24"/>
       <c r="C97" s="22"/>
       <c r="D97" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E97" s="21"/>
+      <c r="E97" s="23"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A98" s="21"/>
-      <c r="B98" s="18"/>
+      <c r="A98" s="23"/>
+      <c r="B98" s="24"/>
       <c r="C98" s="22"/>
       <c r="D98" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="E98" s="21"/>
+      <c r="E98" s="23"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A99" s="20" t="s">
+      <c r="A99" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B99" s="19" t="s">
+      <c r="B99" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="23" t="s">
+      <c r="C99" s="19" t="s">
         <v>213</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E99" s="20" t="s">
+      <c r="E99" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A100" s="20"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="23"/>
+      <c r="A100" s="21"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="19"/>
       <c r="D100" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E100" s="20"/>
+      <c r="E100" s="21"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A101" s="20"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="23"/>
+      <c r="A101" s="21"/>
+      <c r="B101" s="20"/>
+      <c r="C101" s="19"/>
       <c r="D101" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="E101" s="20"/>
+      <c r="E101" s="21"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A102" s="20"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="23"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="19"/>
       <c r="D102" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E102" s="20"/>
+      <c r="E102" s="21"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A103" s="20"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="23"/>
+      <c r="A103" s="21"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="19"/>
       <c r="D103" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E103" s="20"/>
+      <c r="E103" s="21"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A104" s="20"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="23"/>
+      <c r="A104" s="21"/>
+      <c r="B104" s="20"/>
+      <c r="C104" s="19"/>
       <c r="D104" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E104" s="20"/>
+      <c r="E104" s="21"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A105" s="20"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="23"/>
+      <c r="A105" s="21"/>
+      <c r="B105" s="20"/>
+      <c r="C105" s="19"/>
       <c r="D105" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E105" s="20"/>
+      <c r="E105" s="21"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="18" t="s">
+      <c r="B106" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="18" t="s">
+      <c r="C106" s="24" t="s">
         <v>146</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="21" t="s">
+      <c r="E106" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A107" s="21"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="18"/>
+      <c r="A107" s="23"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
       <c r="D107" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="21"/>
+      <c r="E107" s="23"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A108" s="21"/>
-      <c r="B108" s="18"/>
-      <c r="C108" s="18"/>
+      <c r="A108" s="23"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="24"/>
       <c r="D108" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="21"/>
+      <c r="E108" s="23"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A109" s="21"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="18"/>
+      <c r="A109" s="23"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
       <c r="D109" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E109" s="21"/>
+      <c r="E109" s="23"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A110" s="21"/>
-      <c r="B110" s="18"/>
-      <c r="C110" s="18"/>
+      <c r="A110" s="23"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="24"/>
       <c r="D110" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E110" s="21"/>
+      <c r="E110" s="23"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A111" s="21"/>
-      <c r="B111" s="18"/>
-      <c r="C111" s="18"/>
+      <c r="A111" s="23"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
       <c r="D111" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="21"/>
+      <c r="E111" s="23"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A112" s="20" t="s">
+      <c r="A112" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="B112" s="19" t="s">
+      <c r="B112" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C112" s="20" t="s">
         <v>169</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E112" s="20" t="s">
+      <c r="E112" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A113" s="20"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
+      <c r="A113" s="21"/>
+      <c r="B113" s="20"/>
+      <c r="C113" s="20"/>
       <c r="D113" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E113" s="20"/>
+      <c r="E113" s="21"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A114" s="20"/>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
+      <c r="A114" s="21"/>
+      <c r="B114" s="20"/>
+      <c r="C114" s="20"/>
       <c r="D114" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E114" s="20"/>
+      <c r="E114" s="21"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A115" s="20"/>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
+      <c r="A115" s="21"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
       <c r="D115" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E115" s="20"/>
+      <c r="E115" s="21"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A116" s="20"/>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
+      <c r="A116" s="21"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="20"/>
       <c r="D116" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E116" s="20"/>
+      <c r="E116" s="21"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="18" t="s">
+      <c r="C117" s="24" t="s">
         <v>176</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="21" t="s">
+      <c r="E117" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A118" s="21"/>
-      <c r="B118" s="18"/>
-      <c r="C118" s="18"/>
+      <c r="A118" s="23"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="24"/>
       <c r="D118" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="21"/>
+      <c r="E118" s="23"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A119" s="21"/>
-      <c r="B119" s="18"/>
-      <c r="C119" s="18"/>
+      <c r="A119" s="23"/>
+      <c r="B119" s="24"/>
+      <c r="C119" s="24"/>
       <c r="D119" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E119" s="21"/>
+      <c r="E119" s="23"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A120" s="21"/>
-      <c r="B120" s="18"/>
-      <c r="C120" s="18"/>
+      <c r="A120" s="23"/>
+      <c r="B120" s="24"/>
+      <c r="C120" s="24"/>
       <c r="D120" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E120" s="21" t="s">
+      <c r="E120" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A121" s="21"/>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
+      <c r="A121" s="23"/>
+      <c r="B121" s="24"/>
+      <c r="C121" s="24"/>
       <c r="D121" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E121" s="21"/>
+      <c r="E121" s="23"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A122" s="21"/>
-      <c r="B122" s="18"/>
-      <c r="C122" s="18"/>
+      <c r="A122" s="23"/>
+      <c r="B122" s="24"/>
+      <c r="C122" s="24"/>
       <c r="D122" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="E122" s="21"/>
+      <c r="E122" s="23"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A123" s="20" t="s">
+      <c r="A123" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B123" s="19" t="s">
+      <c r="B123" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C123" s="19" t="s">
+      <c r="C123" s="20" t="s">
         <v>184</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E123" s="20" t="s">
+      <c r="E123" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A124" s="20"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
+      <c r="A124" s="21"/>
+      <c r="B124" s="20"/>
+      <c r="C124" s="20"/>
       <c r="D124" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E124" s="20"/>
+      <c r="E124" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B125" s="18" t="s">
+      <c r="B125" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C125" s="18" t="s">
+      <c r="C125" s="24" t="s">
         <v>175</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E125" s="21" t="s">
+      <c r="E125" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A126" s="21"/>
-      <c r="B126" s="18"/>
-      <c r="C126" s="18"/>
+      <c r="A126" s="23"/>
+      <c r="B126" s="24"/>
+      <c r="C126" s="24"/>
       <c r="D126" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E126" s="21"/>
+      <c r="E126" s="23"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A127" s="21"/>
-      <c r="B127" s="18"/>
-      <c r="C127" s="18"/>
+      <c r="A127" s="23"/>
+      <c r="B127" s="24"/>
+      <c r="C127" s="24"/>
       <c r="D127" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E127" s="21" t="s">
+      <c r="E127" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A128" s="21"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="18"/>
+      <c r="A128" s="23"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="24"/>
       <c r="D128" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E128" s="21"/>
+      <c r="E128" s="23"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A129" s="21"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
+      <c r="A129" s="23"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="24"/>
       <c r="D129" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="E129" s="21"/>
+      <c r="E129" s="23"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A130" s="21"/>
-      <c r="B130" s="18"/>
-      <c r="C130" s="18"/>
+      <c r="A130" s="23"/>
+      <c r="B130" s="24"/>
+      <c r="C130" s="24"/>
       <c r="D130" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E130" s="21"/>
+      <c r="E130" s="23"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A131" s="20" t="s">
+      <c r="A131" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="23" t="s">
+      <c r="C131" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E131" s="20" t="s">
+      <c r="E131" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A132" s="20"/>
-      <c r="B132" s="19"/>
-      <c r="C132" s="23"/>
+      <c r="A132" s="21"/>
+      <c r="B132" s="20"/>
+      <c r="C132" s="19"/>
       <c r="D132" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E132" s="20"/>
+      <c r="E132" s="21"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B133" s="18" t="s">
+      <c r="B133" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="18" t="s">
+      <c r="C133" s="24" t="s">
         <v>184</v>
       </c>
       <c r="D133" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E133" s="21" t="s">
+      <c r="E133" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A134" s="21"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
+      <c r="A134" s="23"/>
+      <c r="B134" s="24"/>
+      <c r="C134" s="24"/>
       <c r="D134" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E134" s="21"/>
+      <c r="E134" s="18" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A135" s="20" t="s">
+      <c r="A135" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B135" s="19" t="s">
+      <c r="B135" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="C135" s="19" t="s">
+      <c r="C135" s="20" t="s">
         <v>193</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="E135" s="20" t="s">
+      <c r="E135" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A136" s="20"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
+      <c r="A136" s="21"/>
+      <c r="B136" s="20"/>
+      <c r="C136" s="20"/>
       <c r="D136" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E136" s="20"/>
+      <c r="E136" s="21"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A137" s="20"/>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
+      <c r="A137" s="21"/>
+      <c r="B137" s="20"/>
+      <c r="C137" s="20"/>
       <c r="D137" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="E137" s="20" t="s">
+      <c r="E137" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A138" s="20"/>
-      <c r="B138" s="19"/>
-      <c r="C138" s="19"/>
+      <c r="A138" s="21"/>
+      <c r="B138" s="20"/>
+      <c r="C138" s="20"/>
       <c r="D138" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E138" s="20"/>
+      <c r="E138" s="21"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A139" s="20"/>
-      <c r="B139" s="19"/>
-      <c r="C139" s="19"/>
+      <c r="A139" s="21"/>
+      <c r="B139" s="20"/>
+      <c r="C139" s="20"/>
       <c r="D139" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E139" s="20"/>
+      <c r="E139" s="21"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A140" s="20"/>
-      <c r="B140" s="19"/>
-      <c r="C140" s="19"/>
+      <c r="A140" s="21"/>
+      <c r="B140" s="20"/>
+      <c r="C140" s="20"/>
       <c r="D140" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E140" s="20"/>
+      <c r="E140" s="21"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A141" s="21" t="s">
+      <c r="A141" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="B141" s="18" t="s">
+      <c r="B141" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="22" t="s">
@@ -2956,335 +2963,337 @@
       <c r="D141" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E141" s="21" t="s">
+      <c r="E141" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A142" s="21"/>
-      <c r="B142" s="18"/>
+      <c r="A142" s="23"/>
+      <c r="B142" s="24"/>
       <c r="C142" s="22"/>
       <c r="D142" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E142" s="21"/>
+      <c r="E142" s="23"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A143" s="20" t="s">
+      <c r="A143" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B143" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C143" s="19" t="s">
+      <c r="C143" s="20" t="s">
         <v>184</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E143" s="20" t="s">
+      <c r="E143" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A144" s="20"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="19"/>
+      <c r="A144" s="21"/>
+      <c r="B144" s="20"/>
+      <c r="C144" s="20"/>
       <c r="D144" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E144" s="20"/>
+      <c r="E144" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B145" s="18" t="s">
+      <c r="B145" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="C145" s="18" t="s">
+      <c r="C145" s="24" t="s">
         <v>211</v>
       </c>
       <c r="D145" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E145" s="21" t="s">
+      <c r="E145" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A146" s="21"/>
-      <c r="B146" s="18"/>
-      <c r="C146" s="18"/>
+      <c r="A146" s="23"/>
+      <c r="B146" s="24"/>
+      <c r="C146" s="24"/>
       <c r="D146" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E146" s="21"/>
+      <c r="E146" s="23"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A147" s="21"/>
-      <c r="B147" s="18"/>
-      <c r="C147" s="18"/>
+      <c r="A147" s="23"/>
+      <c r="B147" s="24"/>
+      <c r="C147" s="24"/>
       <c r="D147" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E147" s="21"/>
+      <c r="E147" s="23"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A148" s="21"/>
-      <c r="B148" s="18"/>
-      <c r="C148" s="18"/>
+      <c r="A148" s="23"/>
+      <c r="B148" s="24"/>
+      <c r="C148" s="24"/>
       <c r="D148" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E148" s="21"/>
+      <c r="E148" s="23"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A149" s="21"/>
-      <c r="B149" s="18"/>
-      <c r="C149" s="18"/>
+      <c r="A149" s="23"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
       <c r="D149" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E149" s="21"/>
+      <c r="E149" s="23"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A150" s="21"/>
-      <c r="B150" s="18"/>
-      <c r="C150" s="18"/>
+      <c r="A150" s="23"/>
+      <c r="B150" s="24"/>
+      <c r="C150" s="24"/>
       <c r="D150" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E150" s="21"/>
+      <c r="E150" s="23"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A151" s="21"/>
-      <c r="B151" s="18"/>
-      <c r="C151" s="18"/>
+      <c r="A151" s="23"/>
+      <c r="B151" s="24"/>
+      <c r="C151" s="24"/>
       <c r="D151" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E151" s="21"/>
+      <c r="E151" s="23"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A152" s="20" t="s">
+      <c r="A152" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C152" s="19" t="s">
+      <c r="C152" s="20" t="s">
         <v>212</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E152" s="20" t="s">
+      <c r="E152" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A153" s="20"/>
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
+      <c r="A153" s="21"/>
+      <c r="B153" s="20"/>
+      <c r="C153" s="20"/>
       <c r="D153" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="E153" s="20"/>
+      <c r="E153" s="21"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="B154" s="18" t="s">
+      <c r="B154" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="C154" s="18" t="s">
+      <c r="C154" s="24" t="s">
         <v>230</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E154" s="21" t="s">
+      <c r="E154" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A155" s="21"/>
-      <c r="B155" s="18"/>
-      <c r="C155" s="18"/>
+      <c r="A155" s="23"/>
+      <c r="B155" s="24"/>
+      <c r="C155" s="24"/>
       <c r="D155" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E155" s="21"/>
+      <c r="E155" s="23"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A156" s="20" t="s">
+      <c r="A156" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="B156" s="19" t="s">
+      <c r="B156" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="C156" s="19" t="s">
+      <c r="C156" s="20" t="s">
         <v>229</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E156" s="20" t="s">
+      <c r="E156" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A157" s="20"/>
-      <c r="B157" s="19"/>
-      <c r="C157" s="19"/>
+      <c r="A157" s="21"/>
+      <c r="B157" s="20"/>
+      <c r="C157" s="20"/>
       <c r="D157" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="E157" s="20"/>
+      <c r="E157" s="21"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A158" s="20"/>
-      <c r="B158" s="19"/>
-      <c r="C158" s="19"/>
+      <c r="A158" s="21"/>
+      <c r="B158" s="20"/>
+      <c r="C158" s="20"/>
       <c r="D158" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="E158" s="20"/>
+      <c r="E158" s="21"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A159" s="20"/>
-      <c r="B159" s="19"/>
-      <c r="C159" s="19"/>
+      <c r="A159" s="21"/>
+      <c r="B159" s="20"/>
+      <c r="C159" s="20"/>
       <c r="D159" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E159" s="20"/>
+      <c r="E159" s="21"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A160" s="20"/>
-      <c r="B160" s="19"/>
-      <c r="C160" s="19"/>
+      <c r="A160" s="21"/>
+      <c r="B160" s="20"/>
+      <c r="C160" s="20"/>
       <c r="D160" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="E160" s="20"/>
+      <c r="E160" s="21"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A161" s="20"/>
-      <c r="B161" s="19"/>
-      <c r="C161" s="19"/>
+      <c r="A161" s="21"/>
+      <c r="B161" s="20"/>
+      <c r="C161" s="20"/>
       <c r="D161" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E161" s="20"/>
+      <c r="E161" s="21"/>
     </row>
     <row r="162" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A162" s="20"/>
-      <c r="B162" s="19"/>
-      <c r="C162" s="19"/>
+      <c r="A162" s="21"/>
+      <c r="B162" s="20"/>
+      <c r="C162" s="20"/>
       <c r="D162" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="E162" s="20"/>
+      <c r="E162" s="21"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A163" s="20"/>
-      <c r="B163" s="19"/>
-      <c r="C163" s="19"/>
+      <c r="A163" s="21"/>
+      <c r="B163" s="20"/>
+      <c r="C163" s="20"/>
       <c r="D163" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E163" s="20"/>
+      <c r="E163" s="21"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A164" s="21" t="s">
+      <c r="A164" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="B164" s="18" t="s">
+      <c r="B164" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="C164" s="18" t="s">
+      <c r="C164" s="24" t="s">
         <v>228</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E164" s="21" t="s">
+      <c r="E164" s="23" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A165" s="21"/>
-      <c r="B165" s="18"/>
-      <c r="C165" s="18"/>
+      <c r="A165" s="23"/>
+      <c r="B165" s="24"/>
+      <c r="C165" s="24"/>
       <c r="D165" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E165" s="21"/>
+      <c r="E165" s="23"/>
     </row>
     <row r="166" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A166" s="20" t="s">
+      <c r="A166" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B166" s="19" t="s">
+      <c r="B166" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="C166" s="19" t="s">
+      <c r="C166" s="20" t="s">
         <v>239</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E166" s="20" t="s">
+      <c r="E166" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A167" s="20"/>
-      <c r="B167" s="19"/>
-      <c r="C167" s="19"/>
+      <c r="A167" s="21"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="20"/>
       <c r="D167" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E167" s="20"/>
+      <c r="E167" s="21"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A168" s="20"/>
-      <c r="B168" s="19"/>
-      <c r="C168" s="19"/>
+      <c r="A168" s="21"/>
+      <c r="B168" s="20"/>
+      <c r="C168" s="20"/>
       <c r="D168" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E168" s="20"/>
+      <c r="E168" s="21"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A169" s="20"/>
-      <c r="B169" s="19"/>
-      <c r="C169" s="19"/>
+      <c r="A169" s="21"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="20"/>
       <c r="D169" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="E169" s="20"/>
+      <c r="E169" s="21"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A170" s="20"/>
-      <c r="B170" s="19"/>
-      <c r="C170" s="19"/>
+      <c r="A170" s="21"/>
+      <c r="B170" s="20"/>
+      <c r="C170" s="20"/>
       <c r="D170" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E170" s="20"/>
+      <c r="E170" s="21"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A171" s="20"/>
-      <c r="B171" s="19"/>
-      <c r="C171" s="19"/>
+      <c r="A171" s="21"/>
+      <c r="B171" s="20"/>
+      <c r="C171" s="20"/>
       <c r="D171" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E171" s="20"/>
+      <c r="E171" s="21"/>
     </row>
     <row r="172" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A172" s="2" t="s">
@@ -3321,70 +3330,141 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A175" s="19" t="s">
+      <c r="A175" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B175" s="19"/>
-      <c r="C175" s="19"/>
-      <c r="D175" s="19"/>
-      <c r="E175" s="19"/>
+      <c r="B175" s="20"/>
+      <c r="C175" s="20"/>
+      <c r="D175" s="20"/>
+      <c r="E175" s="20"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A176" s="18" t="s">
+      <c r="A176" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="B176" s="18"/>
-      <c r="C176" s="18"/>
-      <c r="D176" s="18"/>
-      <c r="E176" s="18"/>
+      <c r="B176" s="24"/>
+      <c r="C176" s="24"/>
+      <c r="D176" s="24"/>
+      <c r="E176" s="24"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A177" s="19" t="s">
+      <c r="A177" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="B177" s="19"/>
-      <c r="C177" s="19"/>
-      <c r="D177" s="19"/>
-      <c r="E177" s="19"/>
+      <c r="B177" s="20"/>
+      <c r="C177" s="20"/>
+      <c r="D177" s="20"/>
+      <c r="E177" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="170">
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="E13:E19"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="E36:E38"/>
+  <mergeCells count="167">
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="E166:E171"/>
+    <mergeCell ref="C166:C171"/>
+    <mergeCell ref="B166:B171"/>
+    <mergeCell ref="A166:A171"/>
+    <mergeCell ref="C156:C163"/>
+    <mergeCell ref="B156:B163"/>
+    <mergeCell ref="A156:A163"/>
+    <mergeCell ref="E156:E163"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="E145:E151"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B145:B151"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="B135:B140"/>
+    <mergeCell ref="C135:C140"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="E137:E140"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="B125:B130"/>
+    <mergeCell ref="C125:C130"/>
+    <mergeCell ref="A125:A130"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="E131:E132"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="E125:E126"/>
+    <mergeCell ref="E127:E130"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="C117:C122"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="A117:A122"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="E106:E111"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="E117:E119"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="E85:E87"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="A99:A105"/>
+    <mergeCell ref="B99:B105"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="E99:E105"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="E93:E95"/>
     <mergeCell ref="A62:A71"/>
     <mergeCell ref="B62:B71"/>
     <mergeCell ref="C62:C71"/>
@@ -3409,116 +3489,42 @@
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A55:A59"/>
     <mergeCell ref="B55:B59"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="A99:A105"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="E99:E105"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="E93:E95"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="C117:C122"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="A117:A122"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="E106:E111"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="E117:E119"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="E133:E134"/>
-    <mergeCell ref="B125:B130"/>
-    <mergeCell ref="C125:C130"/>
-    <mergeCell ref="A125:A130"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="E131:E132"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="E125:E126"/>
-    <mergeCell ref="E127:E130"/>
-    <mergeCell ref="A135:A140"/>
-    <mergeCell ref="B135:B140"/>
-    <mergeCell ref="C135:C140"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="E137:E140"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="E145:E151"/>
-    <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B145:B151"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="A177:E177"/>
-    <mergeCell ref="A175:E175"/>
-    <mergeCell ref="E166:E171"/>
-    <mergeCell ref="C166:C171"/>
-    <mergeCell ref="B166:B171"/>
-    <mergeCell ref="A166:A171"/>
-    <mergeCell ref="C156:C163"/>
-    <mergeCell ref="B156:B163"/>
-    <mergeCell ref="A156:A163"/>
-    <mergeCell ref="E156:E163"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B19"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="C13:C19"/>
+    <mergeCell ref="E13:E19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Verification_Plan.xlsx
+++ b/docs/Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niumu\Verification\risc_v_uvc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9002513-0082-41F2-B75F-DFCBFA9FA49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC1A715-B927-435E-8216-CC860B3B6EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10980" xr2:uid="{A1AB3F4A-02CF-4F7B-8A28-0B2275D04914}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="288">
   <si>
     <t>Feature ID</t>
   </si>
@@ -1066,8 +1066,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1076,13 +1076,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1432,7 +1432,7 @@
       <c r="B2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="24" t="s">
         <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1445,7 +1445,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="21"/>
       <c r="B3" s="20"/>
-      <c r="C3" s="19"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1454,7 +1454,7 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="21"/>
       <c r="B4" s="20"/>
-      <c r="C4" s="19"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
@@ -1463,7 +1463,7 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="21"/>
       <c r="B5" s="20"/>
-      <c r="C5" s="19"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
@@ -1472,46 +1472,46 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="21"/>
       <c r="B6" s="20"/>
-      <c r="C6" s="19"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="7" t="s">
         <v>240</v>
       </c>
       <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="22"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="22"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" spans="1:5" ht="24.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" s="21" t="s">
@@ -1520,7 +1520,7 @@
       <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="24" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -1533,7 +1533,7 @@
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" s="21"/>
       <c r="B11" s="20"/>
-      <c r="C11" s="19"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="7" t="s">
         <v>272</v>
       </c>
@@ -1542,82 +1542,82 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="21"/>
       <c r="B12" s="20"/>
-      <c r="C12" s="19"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="7" t="s">
         <v>273</v>
       </c>
       <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>214</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="23"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E15" s="23"/>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="22"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="22"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="23"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="22"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="23"/>
+      <c r="E18" s="22"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="22"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="23"/>
+      <c r="E19" s="22"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="21" t="s">
@@ -1626,7 +1626,7 @@
       <c r="B20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -1639,100 +1639,100 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="19"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="19" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="23"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="23"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="23"/>
+      <c r="E25" s="22"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="23"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="23"/>
+      <c r="E27" s="22"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A28" s="23"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
       <c r="D28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="23"/>
+      <c r="E28" s="22"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
       <c r="D29" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="23"/>
+      <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A30" s="23"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="23"/>
+      <c r="E30" s="22"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="21" t="s">
@@ -1788,39 +1788,39 @@
       <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
       <c r="D37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="23"/>
+      <c r="E37" s="22"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A38" s="23"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
       <c r="D38" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="23"/>
+      <c r="E38" s="22"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="21" t="s">
@@ -1876,39 +1876,39 @@
       <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="19" t="s">
         <v>108</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="19"/>
       <c r="D45" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="23"/>
+      <c r="E45" s="22"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="24"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="19"/>
       <c r="D46" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="23"/>
+      <c r="E46" s="22"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="21" t="s">
@@ -1917,7 +1917,7 @@
       <c r="B47" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="7" t="s">
@@ -1930,37 +1930,37 @@
     <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="21"/>
       <c r="B48" s="20"/>
-      <c r="C48" s="19"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="7" t="s">
         <v>138</v>
       </c>
       <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="19" t="s">
         <v>81</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="23"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
       <c r="D50" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="23"/>
+      <c r="E50" s="22"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="21" t="s">
@@ -2007,57 +2007,57 @@
       <c r="E54" s="21"/>
     </row>
     <row r="55" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="19" t="s">
         <v>72</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="23"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
       <c r="D56" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E56" s="23"/>
+      <c r="E56" s="22"/>
     </row>
     <row r="57" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="23"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
       <c r="D57" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="23"/>
+      <c r="E57" s="22"/>
     </row>
     <row r="58" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="23"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
       <c r="D58" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="23"/>
+      <c r="E58" s="22"/>
     </row>
     <row r="59" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="23"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
       <c r="D59" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="23"/>
+      <c r="E59" s="22"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="21" t="s">
@@ -2066,7 +2066,7 @@
       <c r="B60" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="24" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="7" t="s">
@@ -2079,109 +2079,109 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="21"/>
       <c r="B61" s="20"/>
-      <c r="C61" s="19"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="7" t="s">
         <v>141</v>
       </c>
       <c r="E61" s="21"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="19" t="s">
         <v>98</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="23" t="s">
+      <c r="E62" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A63" s="23"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
       <c r="D63" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E63" s="23"/>
+      <c r="E63" s="22"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A64" s="23"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
       <c r="D64" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="23"/>
+      <c r="E64" s="22"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A65" s="23"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
       <c r="D65" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="23"/>
+      <c r="E65" s="22"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A66" s="23"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
       <c r="D66" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="23"/>
+      <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A67" s="23"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
       <c r="D67" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="23"/>
+      <c r="E67" s="22"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A68" s="23"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
       <c r="D68" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="23"/>
+      <c r="E68" s="22"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A69" s="23"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
+      <c r="A69" s="22"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
       <c r="D69" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="23"/>
+      <c r="E69" s="22"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A70" s="23"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
+      <c r="A70" s="22"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
       <c r="D70" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="23"/>
+      <c r="E70" s="22"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A71" s="23"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
+      <c r="A71" s="22"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
       <c r="D71" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="23"/>
+      <c r="E71" s="22"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="21" t="s">
@@ -2237,39 +2237,39 @@
       <c r="E76" s="21"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="24" t="s">
+      <c r="B77" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="24" t="s">
+      <c r="C77" s="19" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="E77" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A78" s="23"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
       <c r="D78" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="23"/>
+      <c r="E78" s="22"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A79" s="23"/>
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
+      <c r="A79" s="22"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
       <c r="D79" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="23"/>
+      <c r="E79" s="22"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A80" s="21" t="s">
@@ -2325,39 +2325,41 @@
       <c r="E84" s="21"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A85" s="23" t="s">
+      <c r="A85" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="24" t="s">
+      <c r="B85" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="C85" s="19" t="s">
         <v>107</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E85" s="23" t="s">
+      <c r="E85" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A86" s="23"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="19"/>
       <c r="D86" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E86" s="23"/>
+      <c r="E86" s="22"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A87" s="23"/>
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
       <c r="D87" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="E87" s="23"/>
+      <c r="E87" s="18" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A88" s="21" t="s">
@@ -2366,7 +2368,7 @@
       <c r="B88" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" s="24" t="s">
         <v>32</v>
       </c>
       <c r="D88" s="7" t="s">
@@ -2379,46 +2381,46 @@
     <row r="89" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A89" s="21"/>
       <c r="B89" s="20"/>
-      <c r="C89" s="19"/>
+      <c r="C89" s="24"/>
       <c r="D89" s="7" t="s">
         <v>144</v>
       </c>
       <c r="E89" s="21"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="24" t="s">
+      <c r="B90" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="22" t="s">
+      <c r="C90" s="23" t="s">
         <v>277</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A91" s="23"/>
-      <c r="B91" s="24"/>
-      <c r="C91" s="22"/>
+      <c r="A91" s="22"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="23"/>
       <c r="D91" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="23"/>
+      <c r="E91" s="22"/>
     </row>
     <row r="92" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="23"/>
-      <c r="B92" s="24"/>
-      <c r="C92" s="22"/>
+      <c r="A92" s="22"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="23"/>
       <c r="D92" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E92" s="23"/>
+      <c r="E92" s="22"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A93" s="21" t="s">
@@ -2427,7 +2429,7 @@
       <c r="B93" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="24" t="s">
         <v>122</v>
       </c>
       <c r="D93" s="7" t="s">
@@ -2440,7 +2442,7 @@
     <row r="94" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A94" s="21"/>
       <c r="B94" s="20"/>
-      <c r="C94" s="19"/>
+      <c r="C94" s="24"/>
       <c r="D94" s="7" t="s">
         <v>124</v>
       </c>
@@ -2449,46 +2451,46 @@
     <row r="95" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A95" s="21"/>
       <c r="B95" s="20"/>
-      <c r="C95" s="19"/>
+      <c r="C95" s="24"/>
       <c r="D95" s="7" t="s">
         <v>125</v>
       </c>
       <c r="E95" s="21"/>
     </row>
     <row r="96" spans="1:5" ht="30.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="24" t="s">
+      <c r="B96" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="22" t="s">
+      <c r="C96" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="23" t="s">
+      <c r="E96" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="23"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="22"/>
+      <c r="A97" s="22"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="23"/>
       <c r="D97" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E97" s="23"/>
+      <c r="E97" s="22"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A98" s="23"/>
-      <c r="B98" s="24"/>
-      <c r="C98" s="22"/>
+      <c r="A98" s="22"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="23"/>
       <c r="D98" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="E98" s="23"/>
+      <c r="E98" s="22"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A99" s="21" t="s">
@@ -2497,7 +2499,7 @@
       <c r="B99" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="24" t="s">
         <v>213</v>
       </c>
       <c r="D99" s="7" t="s">
@@ -2510,7 +2512,7 @@
     <row r="100" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A100" s="21"/>
       <c r="B100" s="20"/>
-      <c r="C100" s="19"/>
+      <c r="C100" s="24"/>
       <c r="D100" s="7" t="s">
         <v>131</v>
       </c>
@@ -2519,7 +2521,7 @@
     <row r="101" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A101" s="21"/>
       <c r="B101" s="20"/>
-      <c r="C101" s="19"/>
+      <c r="C101" s="24"/>
       <c r="D101" s="7" t="s">
         <v>271</v>
       </c>
@@ -2528,7 +2530,7 @@
     <row r="102" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A102" s="21"/>
       <c r="B102" s="20"/>
-      <c r="C102" s="19"/>
+      <c r="C102" s="24"/>
       <c r="D102" s="7" t="s">
         <v>132</v>
       </c>
@@ -2537,7 +2539,7 @@
     <row r="103" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A103" s="21"/>
       <c r="B103" s="20"/>
-      <c r="C103" s="19"/>
+      <c r="C103" s="24"/>
       <c r="D103" s="7" t="s">
         <v>133</v>
       </c>
@@ -2546,7 +2548,7 @@
     <row r="104" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A104" s="21"/>
       <c r="B104" s="20"/>
-      <c r="C104" s="19"/>
+      <c r="C104" s="24"/>
       <c r="D104" s="7" t="s">
         <v>134</v>
       </c>
@@ -2555,73 +2557,73 @@
     <row r="105" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A105" s="21"/>
       <c r="B105" s="20"/>
-      <c r="C105" s="19"/>
+      <c r="C105" s="24"/>
       <c r="D105" s="7" t="s">
         <v>135</v>
       </c>
       <c r="E105" s="21"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A106" s="23" t="s">
+      <c r="A106" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="24" t="s">
+      <c r="C106" s="19" t="s">
         <v>146</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E106" s="23" t="s">
+      <c r="E106" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A107" s="23"/>
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
+      <c r="A107" s="22"/>
+      <c r="B107" s="19"/>
+      <c r="C107" s="19"/>
       <c r="D107" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="23"/>
+      <c r="E107" s="22"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A108" s="23"/>
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
+      <c r="A108" s="22"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="19"/>
       <c r="D108" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="23"/>
+      <c r="E108" s="22"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A109" s="23"/>
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
+      <c r="A109" s="22"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="19"/>
       <c r="D109" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E109" s="23"/>
+      <c r="E109" s="22"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A110" s="23"/>
-      <c r="B110" s="24"/>
-      <c r="C110" s="24"/>
+      <c r="A110" s="22"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="19"/>
       <c r="D110" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E110" s="23"/>
+      <c r="E110" s="22"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A111" s="23"/>
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
+      <c r="A111" s="22"/>
+      <c r="B111" s="19"/>
+      <c r="C111" s="19"/>
       <c r="D111" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E111" s="23"/>
+      <c r="E111" s="22"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A112" s="21" t="s">
@@ -2677,68 +2679,68 @@
       <c r="E116" s="21"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A117" s="23" t="s">
+      <c r="A117" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="B117" s="24" t="s">
+      <c r="B117" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="24" t="s">
+      <c r="C117" s="19" t="s">
         <v>176</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="23" t="s">
+      <c r="E117" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A118" s="23"/>
-      <c r="B118" s="24"/>
-      <c r="C118" s="24"/>
+      <c r="A118" s="22"/>
+      <c r="B118" s="19"/>
+      <c r="C118" s="19"/>
       <c r="D118" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="23"/>
+      <c r="E118" s="22"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A119" s="23"/>
-      <c r="B119" s="24"/>
-      <c r="C119" s="24"/>
+      <c r="A119" s="22"/>
+      <c r="B119" s="19"/>
+      <c r="C119" s="19"/>
       <c r="D119" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E119" s="23"/>
+      <c r="E119" s="22"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A120" s="23"/>
-      <c r="B120" s="24"/>
-      <c r="C120" s="24"/>
+      <c r="A120" s="22"/>
+      <c r="B120" s="19"/>
+      <c r="C120" s="19"/>
       <c r="D120" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E120" s="23" t="s">
+      <c r="E120" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A121" s="23"/>
-      <c r="B121" s="24"/>
-      <c r="C121" s="24"/>
+      <c r="A121" s="22"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="19"/>
       <c r="D121" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E121" s="23"/>
+      <c r="E121" s="22"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A122" s="23"/>
-      <c r="B122" s="24"/>
-      <c r="C122" s="24"/>
+      <c r="A122" s="22"/>
+      <c r="B122" s="19"/>
+      <c r="C122" s="19"/>
       <c r="D122" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="E122" s="23"/>
+      <c r="E122" s="22"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A123" s="21" t="s">
@@ -2769,68 +2771,68 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A125" s="23" t="s">
+      <c r="A125" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="B125" s="24" t="s">
+      <c r="B125" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C125" s="24" t="s">
+      <c r="C125" s="19" t="s">
         <v>175</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E125" s="23" t="s">
+      <c r="E125" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A126" s="23"/>
-      <c r="B126" s="24"/>
-      <c r="C126" s="24"/>
+      <c r="A126" s="22"/>
+      <c r="B126" s="19"/>
+      <c r="C126" s="19"/>
       <c r="D126" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E126" s="23"/>
+      <c r="E126" s="22"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A127" s="23"/>
-      <c r="B127" s="24"/>
-      <c r="C127" s="24"/>
+      <c r="A127" s="22"/>
+      <c r="B127" s="19"/>
+      <c r="C127" s="19"/>
       <c r="D127" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E127" s="23" t="s">
+      <c r="E127" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A128" s="23"/>
-      <c r="B128" s="24"/>
-      <c r="C128" s="24"/>
+      <c r="A128" s="22"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="19"/>
       <c r="D128" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E128" s="23"/>
+      <c r="E128" s="22"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A129" s="23"/>
-      <c r="B129" s="24"/>
-      <c r="C129" s="24"/>
+      <c r="A129" s="22"/>
+      <c r="B129" s="19"/>
+      <c r="C129" s="19"/>
       <c r="D129" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="E129" s="23"/>
+      <c r="E129" s="22"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A130" s="23"/>
-      <c r="B130" s="24"/>
-      <c r="C130" s="24"/>
+      <c r="A130" s="22"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="19"/>
       <c r="D130" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E130" s="23"/>
+      <c r="E130" s="22"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A131" s="21" t="s">
@@ -2839,7 +2841,7 @@
       <c r="B131" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C131" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="7" t="s">
@@ -2852,20 +2854,20 @@
     <row r="132" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A132" s="21"/>
       <c r="B132" s="20"/>
-      <c r="C132" s="19"/>
+      <c r="C132" s="24"/>
       <c r="D132" s="7" t="s">
         <v>181</v>
       </c>
       <c r="E132" s="21"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A133" s="23" t="s">
+      <c r="A133" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="24" t="s">
+      <c r="C133" s="19" t="s">
         <v>184</v>
       </c>
       <c r="D133" s="8" t="s">
@@ -2876,9 +2878,9 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A134" s="23"/>
-      <c r="B134" s="24"/>
-      <c r="C134" s="24"/>
+      <c r="A134" s="22"/>
+      <c r="B134" s="19"/>
+      <c r="C134" s="19"/>
       <c r="D134" s="8" t="s">
         <v>189</v>
       </c>
@@ -2951,30 +2953,32 @@
       <c r="E140" s="21"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A141" s="23" t="s">
+      <c r="A141" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="B141" s="24" t="s">
+      <c r="B141" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C141" s="22" t="s">
+      <c r="C141" s="23" t="s">
         <v>32</v>
       </c>
       <c r="D141" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E141" s="23" t="s">
-        <v>10</v>
+      <c r="E141" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A142" s="23"/>
-      <c r="B142" s="24"/>
-      <c r="C142" s="22"/>
+      <c r="A142" s="22"/>
+      <c r="B142" s="19"/>
+      <c r="C142" s="23"/>
       <c r="D142" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E142" s="23"/>
+      <c r="E142" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A143" s="21" t="s">
@@ -3005,75 +3009,79 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A145" s="23" t="s">
+      <c r="A145" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B145" s="24" t="s">
+      <c r="B145" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="C145" s="24" t="s">
+      <c r="C145" s="19" t="s">
         <v>211</v>
       </c>
       <c r="D145" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E145" s="23" t="s">
+      <c r="E145" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A146" s="23"/>
-      <c r="B146" s="24"/>
-      <c r="C146" s="24"/>
+      <c r="A146" s="22"/>
+      <c r="B146" s="19"/>
+      <c r="C146" s="19"/>
       <c r="D146" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E146" s="23"/>
+      <c r="E146" s="22"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A147" s="23"/>
-      <c r="B147" s="24"/>
-      <c r="C147" s="24"/>
+      <c r="A147" s="22"/>
+      <c r="B147" s="19"/>
+      <c r="C147" s="19"/>
       <c r="D147" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E147" s="23"/>
+      <c r="E147" s="22"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A148" s="23"/>
-      <c r="B148" s="24"/>
-      <c r="C148" s="24"/>
+      <c r="A148" s="22"/>
+      <c r="B148" s="19"/>
+      <c r="C148" s="19"/>
       <c r="D148" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E148" s="23"/>
+      <c r="E148" s="22"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A149" s="23"/>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
+      <c r="A149" s="22"/>
+      <c r="B149" s="19"/>
+      <c r="C149" s="19"/>
       <c r="D149" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E149" s="23"/>
+      <c r="E149" s="18" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A150" s="23"/>
-      <c r="B150" s="24"/>
-      <c r="C150" s="24"/>
+      <c r="A150" s="22"/>
+      <c r="B150" s="19"/>
+      <c r="C150" s="19"/>
       <c r="D150" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E150" s="23"/>
+      <c r="E150" s="22" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A151" s="23"/>
-      <c r="B151" s="24"/>
-      <c r="C151" s="24"/>
+      <c r="A151" s="22"/>
+      <c r="B151" s="19"/>
+      <c r="C151" s="19"/>
       <c r="D151" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E151" s="23"/>
+      <c r="E151" s="22"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A152" s="21" t="s">
@@ -3102,30 +3110,30 @@
       <c r="E153" s="21"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A154" s="23" t="s">
+      <c r="A154" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="B154" s="24" t="s">
+      <c r="B154" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="C154" s="24" t="s">
+      <c r="C154" s="19" t="s">
         <v>230</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E154" s="23" t="s">
+      <c r="E154" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A155" s="23"/>
-      <c r="B155" s="24"/>
-      <c r="C155" s="24"/>
+      <c r="A155" s="22"/>
+      <c r="B155" s="19"/>
+      <c r="C155" s="19"/>
       <c r="D155" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E155" s="23"/>
+      <c r="E155" s="22"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A156" s="21" t="s">
@@ -3208,30 +3216,30 @@
       <c r="E163" s="21"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A164" s="23" t="s">
+      <c r="A164" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B164" s="24" t="s">
+      <c r="B164" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="C164" s="24" t="s">
+      <c r="C164" s="19" t="s">
         <v>228</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E164" s="23" t="s">
+      <c r="E164" s="22" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A165" s="23"/>
-      <c r="B165" s="24"/>
-      <c r="C165" s="24"/>
+      <c r="A165" s="22"/>
+      <c r="B165" s="19"/>
+      <c r="C165" s="19"/>
       <c r="D165" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E165" s="23"/>
+      <c r="E165" s="22"/>
     </row>
     <row r="166" spans="1:5" ht="14.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A166" s="21" t="s">
@@ -3339,13 +3347,13 @@
       <c r="E175" s="20"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A176" s="24" t="s">
+      <c r="A176" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="B176" s="24"/>
-      <c r="C176" s="24"/>
-      <c r="D176" s="24"/>
-      <c r="E176" s="24"/>
+      <c r="B176" s="19"/>
+      <c r="C176" s="19"/>
+      <c r="D176" s="19"/>
+      <c r="E176" s="19"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A177" s="20" t="s">
@@ -3358,121 +3366,37 @@
     </row>
   </sheetData>
   <mergeCells count="167">
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="A177:E177"/>
-    <mergeCell ref="A175:E175"/>
-    <mergeCell ref="E166:E171"/>
-    <mergeCell ref="C166:C171"/>
-    <mergeCell ref="B166:B171"/>
-    <mergeCell ref="A166:A171"/>
-    <mergeCell ref="C156:C163"/>
-    <mergeCell ref="B156:B163"/>
-    <mergeCell ref="A156:A163"/>
-    <mergeCell ref="E156:E163"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="E145:E151"/>
-    <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B145:B151"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="A135:A140"/>
-    <mergeCell ref="B135:B140"/>
-    <mergeCell ref="C135:C140"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="E137:E140"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="B125:B130"/>
-    <mergeCell ref="C125:C130"/>
-    <mergeCell ref="A125:A130"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="E131:E132"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="E125:E126"/>
-    <mergeCell ref="E127:E130"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="C117:C122"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="A117:A122"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="E106:E111"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="E117:E119"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="A99:A105"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="E99:E105"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="E93:E95"/>
-    <mergeCell ref="A62:A71"/>
-    <mergeCell ref="B62:B71"/>
-    <mergeCell ref="C62:C71"/>
-    <mergeCell ref="E62:E71"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="B13:B19"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="C13:C19"/>
+    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="E145:E148"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="E10:E12"/>
     <mergeCell ref="C22:C30"/>
     <mergeCell ref="E22:E30"/>
     <mergeCell ref="A22:A30"/>
@@ -3497,34 +3421,118 @@
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="C39:C43"/>
     <mergeCell ref="E39:E43"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="A62:A71"/>
+    <mergeCell ref="B62:B71"/>
+    <mergeCell ref="C62:C71"/>
+    <mergeCell ref="E62:E71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="E106:E111"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="E117:E119"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="A99:A105"/>
+    <mergeCell ref="B99:B105"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="E99:E105"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="E131:E132"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="E125:E126"/>
+    <mergeCell ref="E127:E130"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="C117:C122"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="A117:A122"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="B125:B130"/>
+    <mergeCell ref="C125:C130"/>
+    <mergeCell ref="A125:A130"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="B135:B140"/>
+    <mergeCell ref="C135:C140"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="E137:E140"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B145:B151"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="E166:E171"/>
+    <mergeCell ref="C166:C171"/>
+    <mergeCell ref="B166:B171"/>
+    <mergeCell ref="A166:A171"/>
+    <mergeCell ref="C156:C163"/>
+    <mergeCell ref="B156:B163"/>
+    <mergeCell ref="A156:A163"/>
+    <mergeCell ref="E156:E163"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A164:A165"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
